--- a/google_data/Pobočky/Výroba/Databaze Výroba 2026.xlsx
+++ b/google_data/Pobočky/Výroba/Databaze Výroba 2026.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2641" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2681" uniqueCount="211">
   <si>
     <t>Datum</t>
   </si>
@@ -106,12 +106,24 @@
     <t>Středa</t>
   </si>
   <si>
+    <t>04.06.2026</t>
+  </si>
+  <si>
+    <t>Čtvrtek</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>05.06.2026</t>
+  </si>
+  <si>
+    <t>Pátek</t>
+  </si>
+  <si>
     <t>01.05.2026</t>
   </si>
   <si>
-    <t>Pátek</t>
-  </si>
-  <si>
     <t>Stepanenko Solomiia</t>
   </si>
   <si>
@@ -137,12 +149,6 @@
   </si>
   <si>
     <t>07.05.2026</t>
-  </si>
-  <si>
-    <t>Čtvrtek</t>
-  </si>
-  <si>
-    <t>18:00</t>
   </si>
   <si>
     <t>08.05.2026</t>
@@ -1190,6 +1196,148 @@
         <v>42796.0</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="3">
+        <v>42280.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" s="3">
+        <v>40484.25</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1239,10 +1387,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>13</v>
@@ -1259,13 +1407,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -1279,10 +1427,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>17</v>
@@ -1299,10 +1447,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H5" s="3">
         <v>42112.0</v>
@@ -1310,10 +1458,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>23</v>
@@ -1330,10 +1478,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H7" s="3">
         <v>40004.0</v>
@@ -1341,10 +1489,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H8" s="3">
         <v>40004.0</v>
@@ -1352,7 +1500,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -1372,13 +1520,13 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -1392,7 +1540,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>12</v>
@@ -1412,7 +1560,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>12</v>
@@ -1423,13 +1571,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>14</v>
@@ -1443,7 +1591,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>19</v>
@@ -1463,7 +1611,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>19</v>
@@ -1483,7 +1631,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>19</v>
@@ -1494,7 +1642,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>28</v>
@@ -1514,13 +1662,13 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>14</v>
@@ -1534,7 +1682,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>28</v>
@@ -1545,10 +1693,10 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>13</v>
@@ -1565,13 +1713,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>14</v>
@@ -1585,10 +1733,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>17</v>
@@ -1605,10 +1753,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>23</v>
@@ -1617,7 +1765,7 @@
         <v>24</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>21</v>
@@ -1625,10 +1773,10 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H24" s="3">
         <v>40132.0</v>
@@ -1636,30 +1784,30 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>17</v>
@@ -1668,18 +1816,18 @@
         <v>14</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H27" s="3">
         <v>40148.0</v>
@@ -1687,31 +1835,31 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H29" s="3"/>
       <c r="P29" s="3">
@@ -1742,7 +1890,7 @@
         <v>0.0</v>
       </c>
       <c r="AD29" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AI29" s="3">
         <v>0.0</v>
@@ -1789,10 +1937,10 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H30" s="3">
         <v>40004.0</v>
@@ -1800,13 +1948,13 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>14</v>
@@ -1820,7 +1968,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -1840,7 +1988,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>12</v>
@@ -1851,27 +1999,27 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>19</v>
@@ -1883,15 +2031,15 @@
         <v>14</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>19</v>
@@ -1911,7 +2059,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>19</v>
@@ -1922,13 +2070,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>14</v>
@@ -1942,7 +2090,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>28</v>
@@ -1962,7 +2110,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>28</v>
@@ -1973,13 +2121,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>14</v>
@@ -1993,10 +2141,10 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>17</v>
@@ -2013,10 +2161,10 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>23</v>
@@ -2025,7 +2173,7 @@
         <v>24</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>21</v>
@@ -2033,10 +2181,10 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H44" s="3">
         <v>41356.0</v>
@@ -2044,13 +2192,13 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>14</v>
@@ -2064,10 +2212,10 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>17</v>
@@ -2084,10 +2232,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H47" s="3">
         <v>40900.0</v>
@@ -2095,10 +2243,10 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H48" s="3">
         <v>40004.0</v>
@@ -2106,10 +2254,10 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H49" s="3">
         <v>40004.0</v>
@@ -2117,7 +2265,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>12</v>
@@ -2137,13 +2285,13 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>14</v>
@@ -2157,7 +2305,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>12</v>
@@ -2168,7 +2316,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>19</v>
@@ -2188,13 +2336,13 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>14</v>
@@ -2208,7 +2356,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>19</v>
@@ -2228,7 +2376,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>19</v>
@@ -2248,7 +2396,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>19</v>
@@ -2259,13 +2407,13 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>14</v>
@@ -2279,7 +2427,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>28</v>
@@ -2299,7 +2447,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>28</v>
@@ -2319,7 +2467,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>28</v>
@@ -2330,13 +2478,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>14</v>
@@ -2350,10 +2498,10 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>13</v>
@@ -2370,10 +2518,10 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>17</v>
@@ -2390,10 +2538,10 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>23</v>
@@ -2402,7 +2550,7 @@
         <v>24</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>21</v>
@@ -2410,10 +2558,10 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H66" s="3">
         <v>41823.0</v>
@@ -2421,10 +2569,10 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>13</v>
@@ -2441,13 +2589,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>14</v>
@@ -2461,10 +2609,10 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>17</v>
@@ -2481,10 +2629,10 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H70" s="3">
         <v>41608.0</v>
@@ -2492,10 +2640,10 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>23</v>
@@ -2512,10 +2660,10 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H72" s="3">
         <v>40928.0</v>
@@ -2523,10 +2671,10 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H73" s="3">
         <v>40004.0</v>
@@ -2534,7 +2682,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>12</v>
@@ -2554,7 +2702,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>12</v>
@@ -2574,7 +2722,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>12</v>
@@ -2585,7 +2733,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>19</v>
@@ -2605,7 +2753,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>19</v>
@@ -2625,7 +2773,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>19</v>
@@ -2645,7 +2793,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>19</v>
@@ -2656,7 +2804,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>28</v>
@@ -2676,7 +2824,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>28</v>
@@ -2696,7 +2844,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>28</v>
@@ -2707,10 +2855,10 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>13</v>
@@ -2727,10 +2875,10 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>17</v>
@@ -2747,10 +2895,10 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>23</v>
@@ -2759,7 +2907,7 @@
         <v>24</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>21</v>
@@ -2767,10 +2915,10 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H87" s="3">
         <v>41988.0</v>
@@ -2778,10 +2926,10 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>13</v>
@@ -2798,10 +2946,10 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>17</v>
@@ -2818,10 +2966,10 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H90" s="3">
         <v>41143.0</v>
@@ -2829,10 +2977,10 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>23</v>
@@ -2849,10 +2997,10 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H92" s="3">
         <v>41564.0</v>
@@ -2860,10 +3008,10 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H93" s="3">
         <v>40004.0</v>
@@ -2918,7 +3066,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>28</v>
@@ -2938,13 +3086,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -2958,7 +3106,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>28</v>
@@ -2978,7 +3126,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>28</v>
@@ -2989,10 +3137,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>13</v>
@@ -3009,13 +3157,13 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>14</v>
@@ -3029,10 +3177,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>17</v>
@@ -3049,10 +3197,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>23</v>
@@ -3061,7 +3209,7 @@
         <v>24</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>21</v>
@@ -3069,10 +3217,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H10" s="3">
         <v>40132.0</v>
@@ -3080,10 +3228,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>13</v>
@@ -3100,13 +3248,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -3120,10 +3268,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>17</v>
@@ -3140,10 +3288,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H14" s="3">
         <v>40260.0</v>
@@ -3151,10 +3299,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>23</v>
@@ -3171,10 +3319,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H16" s="3">
         <v>40100.0</v>
@@ -3182,10 +3330,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H17" s="3">
         <v>40004.0</v>
@@ -3193,7 +3341,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>12</v>
@@ -3213,13 +3361,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>14</v>
@@ -3233,7 +3381,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>12</v>
@@ -3253,7 +3401,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>12</v>
@@ -3264,7 +3412,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>19</v>
@@ -3284,13 +3432,13 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>14</v>
@@ -3304,7 +3452,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>19</v>
@@ -3324,13 +3472,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>24</v>
@@ -3339,12 +3487,12 @@
         <v>15</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>19</v>
@@ -3359,12 +3507,12 @@
         <v>25</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>19</v>
@@ -3375,7 +3523,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>28</v>
@@ -3395,13 +3543,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>14</v>
@@ -3415,7 +3563,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>28</v>
@@ -3435,7 +3583,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>28</v>
@@ -3446,10 +3594,10 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>13</v>
@@ -3466,13 +3614,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>14</v>
@@ -3486,10 +3634,10 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>17</v>
@@ -3506,10 +3654,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>23</v>
@@ -3518,7 +3666,7 @@
         <v>24</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>21</v>
@@ -3526,10 +3674,10 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H36" s="3">
         <v>41040.0</v>
@@ -3537,10 +3685,10 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>13</v>
@@ -3549,38 +3697,38 @@
         <v>14</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>17</v>
@@ -3589,18 +3737,18 @@
         <v>14</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H40" s="3">
         <v>40788.0</v>
@@ -3608,10 +3756,10 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>23</v>
@@ -3628,10 +3776,10 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H42" s="3">
         <v>40502.0</v>
@@ -3639,10 +3787,10 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H43" s="3">
         <v>40004.0</v>
@@ -3650,7 +3798,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>12</v>
@@ -3662,15 +3810,15 @@
         <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>12</v>
@@ -3682,15 +3830,15 @@
         <v>14</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>12</v>
@@ -3701,7 +3849,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>19</v>
@@ -3721,7 +3869,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>19</v>
@@ -3741,19 +3889,19 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>14</v>
@@ -3761,7 +3909,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>19</v>
@@ -3770,10 +3918,10 @@
         <v>23</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>14</v>
@@ -3781,7 +3929,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>19</v>
@@ -3792,13 +3940,13 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>14</v>
@@ -3812,7 +3960,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>28</v>
@@ -3832,7 +3980,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>28</v>
@@ -3852,7 +4000,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>28</v>
@@ -3863,10 +4011,10 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>13</v>
@@ -3883,13 +4031,13 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>14</v>
@@ -3903,10 +4051,10 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>17</v>
@@ -3923,10 +4071,10 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>23</v>
@@ -3935,7 +4083,7 @@
         <v>24</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>21</v>
@@ -3943,10 +4091,10 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H60" s="3">
         <v>41856.0</v>
@@ -3954,10 +4102,10 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>13</v>
@@ -3974,13 +4122,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>14</v>
@@ -3994,10 +4142,10 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H63" s="3">
         <v>40636.0</v>
@@ -4005,10 +4153,10 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>23</v>
@@ -4025,10 +4173,10 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H65" s="3">
         <v>40970.0</v>
@@ -4036,10 +4184,10 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H66" s="3">
         <v>40004.0</v>
@@ -4047,7 +4195,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>12</v>
@@ -4067,13 +4215,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>14</v>
@@ -4087,7 +4235,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>12</v>
@@ -4098,7 +4246,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>19</v>
@@ -4118,13 +4266,13 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>14</v>
@@ -4138,19 +4286,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>14</v>
@@ -4158,7 +4306,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>19</v>
@@ -4167,18 +4315,18 @@
         <v>23</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>19</v>
@@ -4189,7 +4337,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>28</v>
@@ -4209,13 +4357,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>14</v>
@@ -4229,7 +4377,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>28</v>
@@ -4240,10 +4388,10 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>13</v>
@@ -4260,13 +4408,13 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>14</v>
@@ -4280,10 +4428,10 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>23</v>
@@ -4292,7 +4440,7 @@
         <v>24</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>21</v>
@@ -4300,10 +4448,10 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H81" s="3">
         <v>40004.0</v>
@@ -4311,10 +4459,10 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>13</v>
@@ -4331,13 +4479,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>14</v>
@@ -4351,10 +4499,10 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H84" s="3">
         <v>41015.5</v>
@@ -4362,10 +4510,10 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>23</v>
@@ -4382,10 +4530,10 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H86" s="3">
         <v>41270.0</v>
@@ -4393,10 +4541,10 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H87" s="3">
         <v>40004.0</v>
@@ -4404,7 +4552,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>12</v>
@@ -4424,13 +4572,13 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>14</v>
@@ -4444,7 +4592,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>12</v>
@@ -4455,7 +4603,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>19</v>
@@ -4475,7 +4623,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>19</v>
@@ -4495,27 +4643,27 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>19</v>
@@ -4524,18 +4672,18 @@
         <v>23</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>19</v>
@@ -4546,7 +4694,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>28</v>
@@ -4566,13 +4714,13 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>14</v>
@@ -4586,7 +4734,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>28</v>
@@ -4597,10 +4745,10 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>13</v>
@@ -4617,13 +4765,13 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>14</v>
@@ -4637,10 +4785,10 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>17</v>
@@ -4657,10 +4805,10 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>23</v>
@@ -4669,7 +4817,7 @@
         <v>24</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>21</v>
@@ -4677,10 +4825,10 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H103" s="3">
         <v>43072.0</v>
@@ -4735,24 +4883,24 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H3" s="3">
         <v>40004.0</v>
@@ -4760,7 +4908,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -4780,13 +4928,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
@@ -4800,7 +4948,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
@@ -4820,7 +4968,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -4831,7 +4979,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
@@ -4851,13 +4999,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>14</v>
@@ -4871,7 +5019,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>19</v>
@@ -4883,15 +5031,15 @@
         <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>19</v>
@@ -4911,7 +5059,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>19</v>
@@ -4922,7 +5070,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>28</v>
@@ -4942,13 +5090,13 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
@@ -4962,7 +5110,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>28</v>
@@ -4982,7 +5130,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>28</v>
@@ -4993,10 +5141,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>13</v>
@@ -5013,30 +5161,30 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>17</v>
@@ -5045,18 +5193,18 @@
         <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>23</v>
@@ -5065,7 +5213,7 @@
         <v>24</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>21</v>
@@ -5073,10 +5221,10 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -5086,15 +5234,15 @@
         <v>40483.5</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -5128,7 +5276,7 @@
         <v>0.0</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AI22" s="3">
         <v>0.0</v>
@@ -5175,10 +5323,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>13</v>
@@ -5195,13 +5343,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>14</v>
@@ -5215,10 +5363,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>17</v>
@@ -5235,10 +5383,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H26" s="3">
         <v>40452.0</v>
@@ -5246,10 +5394,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>23</v>
@@ -5266,24 +5414,24 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H29" s="3">
         <v>40400.0</v>
@@ -5291,24 +5439,24 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H31" s="3">
         <v>40004.0</v>
@@ -5316,7 +5464,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -5336,13 +5484,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>14</v>
@@ -5356,7 +5504,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>12</v>
@@ -5376,7 +5524,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>12</v>
@@ -5387,7 +5535,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>19</v>
@@ -5407,27 +5555,27 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>19</v>
@@ -5447,7 +5595,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>19</v>
@@ -5467,7 +5615,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>19</v>
@@ -5480,12 +5628,12 @@
         <v>41160.0</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>19</v>
@@ -5522,7 +5670,7 @@
         <v>0.0</v>
       </c>
       <c r="AD41" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AI41" s="3">
         <v>0.0</v>
@@ -5569,7 +5717,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>28</v>
@@ -5589,13 +5737,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>14</v>
@@ -5609,7 +5757,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>28</v>
@@ -5629,7 +5777,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>28</v>
@@ -5640,10 +5788,10 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>13</v>
@@ -5660,30 +5808,30 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>17</v>
@@ -5692,18 +5840,18 @@
         <v>14</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>23</v>
@@ -5712,7 +5860,7 @@
         <v>24</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>21</v>
@@ -5720,10 +5868,10 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -5733,15 +5881,15 @@
         <v>41286.0</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -5775,7 +5923,7 @@
         <v>0.0</v>
       </c>
       <c r="AD51" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AI51" s="3">
         <v>0.0</v>
@@ -5822,10 +5970,10 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>13</v>
@@ -5842,13 +5990,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>14</v>
@@ -5862,10 +6010,10 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>17</v>
@@ -5882,10 +6030,10 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H55" s="3">
         <v>41060.0</v>
@@ -5893,10 +6041,10 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>23</v>
@@ -5913,24 +6061,24 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H58" s="3">
         <v>40784.0</v>
@@ -5938,24 +6086,24 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H60" s="3">
         <v>40004.0</v>
@@ -5963,7 +6111,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>12</v>
@@ -5983,13 +6131,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>14</v>
@@ -6003,7 +6151,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>12</v>
@@ -6023,7 +6171,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>12</v>
@@ -6034,7 +6182,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>19</v>
@@ -6054,13 +6202,13 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>14</v>
@@ -6074,7 +6222,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>19</v>
@@ -6094,7 +6242,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>19</v>
@@ -6114,7 +6262,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>19</v>
@@ -6125,7 +6273,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>28</v>
@@ -6145,27 +6293,27 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>28</v>
@@ -6177,15 +6325,15 @@
         <v>14</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>28</v>
@@ -6198,12 +6346,12 @@
         <v>41264.0</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>28</v>
@@ -6240,7 +6388,7 @@
         <v>0.0</v>
       </c>
       <c r="AD74" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AI74" s="3">
         <v>0.0</v>
@@ -6287,10 +6435,10 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>13</v>
@@ -6307,13 +6455,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>14</v>
@@ -6327,10 +6475,10 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>23</v>
@@ -6339,7 +6487,7 @@
         <v>24</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>21</v>
@@ -6347,10 +6495,10 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H78" s="3">
         <v>41616.0</v>
@@ -6358,10 +6506,10 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>13</v>
@@ -6378,13 +6526,13 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>14</v>
@@ -6398,10 +6546,10 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>17</v>
@@ -6418,10 +6566,10 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H82" s="3">
         <v>41620.0</v>
@@ -6429,10 +6577,10 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>23</v>
@@ -6449,24 +6597,24 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H85" s="3">
         <v>41324.0</v>
@@ -6474,24 +6622,24 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H87" s="3">
         <v>40004.0</v>
@@ -6499,7 +6647,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>12</v>
@@ -6519,13 +6667,13 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>14</v>
@@ -6539,7 +6687,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>12</v>
@@ -6550,7 +6698,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>19</v>
@@ -6570,21 +6718,21 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>19</v>
@@ -6604,7 +6752,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>19</v>
@@ -6624,7 +6772,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>19</v>
@@ -6635,7 +6783,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>28</v>
@@ -6655,13 +6803,13 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>14</v>
@@ -6675,7 +6823,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>28</v>
@@ -6695,7 +6843,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>28</v>
@@ -6706,10 +6854,10 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>13</v>
@@ -6726,13 +6874,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>14</v>
@@ -6746,10 +6894,10 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>17</v>
@@ -6766,10 +6914,10 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>23</v>
@@ -6778,7 +6926,7 @@
         <v>24</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>21</v>
@@ -6786,10 +6934,10 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H104" s="3">
         <v>43076.0</v>
@@ -6797,10 +6945,10 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>13</v>
@@ -6817,13 +6965,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>14</v>
@@ -6837,10 +6985,10 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>17</v>
@@ -6857,10 +7005,10 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H108" s="3">
         <v>42132.0</v>
@@ -6868,10 +7016,10 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>23</v>
@@ -6888,24 +7036,24 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H111" s="3">
         <v>41708.0</v>
@@ -6913,24 +7061,24 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H113" s="3">
         <v>40004.0</v>
@@ -6938,7 +7086,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>12</v>
@@ -6958,13 +7106,13 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>14</v>
@@ -6978,7 +7126,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>12</v>
@@ -6998,7 +7146,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>12</v>
@@ -7009,7 +7157,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>19</v>
@@ -7029,13 +7177,13 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>14</v>
@@ -7049,7 +7197,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>19</v>
@@ -7069,19 +7217,19 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>14</v>
@@ -7089,7 +7237,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>19</v>
@@ -7098,7 +7246,7 @@
         <v>23</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>25</v>
@@ -7109,7 +7257,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>19</v>
@@ -7167,24 +7315,24 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H3" s="3">
         <v>40004.0</v>
@@ -7192,7 +7340,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -7212,13 +7360,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
@@ -7232,7 +7380,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
@@ -7252,7 +7400,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -7263,7 +7411,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
@@ -7275,35 +7423,35 @@
         <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>19</v>
@@ -7315,15 +7463,15 @@
         <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>19</v>
@@ -7343,7 +7491,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>19</v>
@@ -7354,7 +7502,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>28</v>
@@ -7366,35 +7514,35 @@
         <v>14</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>28</v>
@@ -7405,10 +7553,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>13</v>
@@ -7417,38 +7565,38 @@
         <v>14</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>23</v>
@@ -7457,7 +7605,7 @@
         <v>24</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>21</v>
@@ -7465,10 +7613,10 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H19" s="3">
         <v>40415.5</v>
@@ -7476,10 +7624,10 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>13</v>
@@ -7496,13 +7644,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>14</v>
@@ -7516,10 +7664,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>17</v>
@@ -7536,10 +7684,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H23" s="3">
         <v>40380.0</v>
@@ -7547,10 +7695,10 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>23</v>
@@ -7567,24 +7715,24 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H26" s="3">
         <v>40400.0</v>
@@ -7592,24 +7740,24 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H28" s="3">
         <v>40004.0</v>
@@ -7617,7 +7765,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>12</v>
@@ -7637,13 +7785,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>14</v>
@@ -7657,7 +7805,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>12</v>
@@ -7677,7 +7825,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -7688,7 +7836,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>19</v>
@@ -7700,35 +7848,35 @@
         <v>14</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>19</v>
@@ -7740,15 +7888,15 @@
         <v>14</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>19</v>
@@ -7768,7 +7916,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>19</v>
@@ -7779,7 +7927,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>28</v>
@@ -7799,13 +7947,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>14</v>
@@ -7819,7 +7967,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>28</v>
@@ -7839,7 +7987,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>28</v>
@@ -7850,10 +7998,10 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>13</v>
@@ -7862,38 +8010,38 @@
         <v>14</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>17</v>
@@ -7902,18 +8050,18 @@
         <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>23</v>
@@ -7922,7 +8070,7 @@
         <v>24</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>21</v>
@@ -7930,10 +8078,10 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H46" s="3">
         <v>41168.5</v>
@@ -7941,10 +8089,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>17</v>
@@ -7953,38 +8101,38 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H49" s="3">
         <v>40858.0</v>
@@ -7992,10 +8140,10 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>23</v>
@@ -8012,24 +8160,24 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H52" s="3">
         <v>40784.0</v>
@@ -8037,24 +8185,24 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H54" s="3">
         <v>40004.0</v>
@@ -8062,7 +8210,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>12</v>
@@ -8074,35 +8222,35 @@
         <v>14</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>12</v>
@@ -8114,15 +8262,15 @@
         <v>14</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>12</v>
@@ -8133,7 +8281,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>19</v>
@@ -8153,13 +8301,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>14</v>
@@ -8173,7 +8321,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>19</v>
@@ -8193,7 +8341,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>19</v>
@@ -8202,18 +8350,18 @@
         <v>23</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>19</v>
@@ -8224,7 +8372,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>28</v>
@@ -8244,13 +8392,13 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>14</v>
@@ -8264,7 +8412,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>28</v>
@@ -8284,7 +8432,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>28</v>
@@ -8295,10 +8443,10 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>13</v>
@@ -8307,38 +8455,38 @@
         <v>14</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>17</v>
@@ -8347,18 +8495,18 @@
         <v>14</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>23</v>
@@ -8367,7 +8515,7 @@
         <v>24</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>21</v>
@@ -8375,10 +8523,10 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H72" s="3">
         <v>42114.0</v>
@@ -8386,10 +8534,10 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>13</v>
@@ -8406,13 +8554,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>14</v>
@@ -8426,10 +8574,10 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>17</v>
@@ -8446,10 +8594,10 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H76" s="3">
         <v>41604.0</v>
@@ -8457,10 +8605,10 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>23</v>
@@ -8477,24 +8625,24 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H79" s="3">
         <v>41312.0</v>
@@ -8502,24 +8650,24 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H81" s="3">
         <v>40004.0</v>
@@ -8527,7 +8675,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>12</v>
@@ -8547,13 +8695,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>14</v>
@@ -8567,7 +8715,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>12</v>
@@ -8587,7 +8735,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>12</v>
@@ -8598,7 +8746,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>19</v>
@@ -8618,13 +8766,13 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>14</v>
@@ -8638,7 +8786,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>19</v>
@@ -8658,7 +8806,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>19</v>
@@ -8678,7 +8826,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>19</v>
@@ -8689,7 +8837,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>28</v>
@@ -8709,13 +8857,13 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>14</v>
@@ -8729,7 +8877,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>28</v>
@@ -8749,7 +8897,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>28</v>
@@ -8760,10 +8908,10 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>13</v>
@@ -8772,32 +8920,32 @@
         <v>14</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>17</v>
@@ -8806,18 +8954,18 @@
         <v>14</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>23</v>
@@ -8826,7 +8974,7 @@
         <v>24</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>21</v>
@@ -8834,10 +8982,10 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H99" s="3">
         <v>41929.0</v>
@@ -8845,10 +8993,10 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>13</v>
@@ -8865,13 +9013,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>14</v>
@@ -8885,10 +9033,10 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>17</v>
@@ -8905,10 +9053,10 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H103" s="3">
         <v>41630.0</v>
@@ -8916,24 +9064,24 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>23</v>
@@ -8950,10 +9098,10 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H106" s="3">
         <v>41696.0</v>
@@ -9008,24 +9156,24 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H3" s="3">
         <v>40004.0</v>
@@ -9033,30 +9181,30 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>17</v>
@@ -9065,38 +9213,38 @@
         <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H7" s="3">
         <v>40004.0</v>
@@ -9104,10 +9252,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>23</v>
@@ -9124,24 +9272,24 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H10" s="3">
         <v>40004.0</v>
@@ -9149,24 +9297,24 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H12" s="3">
         <v>40004.0</v>
@@ -9174,7 +9322,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
@@ -9194,7 +9342,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
@@ -9214,13 +9362,13 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>14</v>
@@ -9234,7 +9382,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>12</v>
@@ -9245,7 +9393,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>19</v>
@@ -9265,7 +9413,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>19</v>
@@ -9285,13 +9433,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>14</v>
@@ -9305,7 +9453,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>19</v>
@@ -9325,7 +9473,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>19</v>
@@ -9336,7 +9484,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>28</v>
@@ -9356,7 +9504,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>28</v>
@@ -9376,13 +9524,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>14</v>
@@ -9396,7 +9544,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>28</v>
@@ -9407,10 +9555,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>13</v>
@@ -9427,10 +9575,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>17</v>
@@ -9447,13 +9595,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>14</v>
@@ -9467,10 +9615,10 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>23</v>
@@ -9479,18 +9627,18 @@
         <v>24</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H30" s="3">
         <v>40004.0</v>
@@ -9498,10 +9646,10 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>17</v>
@@ -9518,13 +9666,13 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>14</v>
@@ -9538,10 +9686,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>13</v>
@@ -9558,10 +9706,10 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H34" s="3">
         <v>40644.0</v>
@@ -9569,10 +9717,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>23</v>
@@ -9589,24 +9737,24 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H37" s="3">
         <v>40532.0</v>
@@ -9614,24 +9762,24 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H39" s="3">
         <v>40004.0</v>
@@ -9639,7 +9787,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>12</v>
@@ -9659,13 +9807,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>14</v>
@@ -9679,7 +9827,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>12</v>
@@ -9690,7 +9838,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>19</v>
@@ -9702,35 +9850,35 @@
         <v>14</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>19</v>
@@ -9750,7 +9898,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>19</v>
@@ -9761,7 +9909,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>28</v>
@@ -9773,35 +9921,35 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>28</v>
@@ -9812,10 +9960,10 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>13</v>
@@ -9824,38 +9972,38 @@
         <v>14</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>17</v>
@@ -9867,15 +10015,15 @@
         <v>24</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>23</v>
@@ -9884,18 +10032,18 @@
         <v>24</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H54" s="3">
         <v>41250.0</v>
@@ -9903,10 +10051,10 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>13</v>
@@ -9923,13 +10071,13 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>14</v>
@@ -9943,10 +10091,10 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>17</v>
@@ -9963,10 +10111,10 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H58" s="3">
         <v>41212.0</v>
@@ -9974,10 +10122,10 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>23</v>
@@ -9994,24 +10142,24 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H61" s="3">
         <v>40904.0</v>
@@ -10019,24 +10167,24 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H63" s="3">
         <v>40004.0</v>
@@ -10044,7 +10192,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>12</v>
@@ -10064,13 +10212,13 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>14</v>
@@ -10084,7 +10232,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>12</v>
@@ -10095,7 +10243,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>19</v>
@@ -10115,13 +10263,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>14</v>
@@ -10135,7 +10283,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>19</v>
@@ -10155,7 +10303,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>19</v>
@@ -10175,7 +10323,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>19</v>
@@ -10186,7 +10334,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>28</v>
@@ -10198,35 +10346,35 @@
         <v>14</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>28</v>
@@ -10241,12 +10389,12 @@
         <v>21</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>28</v>
@@ -10257,10 +10405,10 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>13</v>
@@ -10277,13 +10425,13 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>14</v>
@@ -10297,10 +10445,10 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>23</v>
@@ -10309,7 +10457,7 @@
         <v>24</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>21</v>
@@ -10317,10 +10465,10 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H79" s="3">
         <v>41784.0</v>
@@ -10328,10 +10476,10 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>13</v>
@@ -10340,38 +10488,38 @@
         <v>14</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H82" s="3">
         <v>40833.5</v>
@@ -10379,10 +10527,10 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>23</v>
@@ -10399,10 +10547,10 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H84" s="3">
         <v>41444.0</v>
@@ -10410,10 +10558,10 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H85" s="3">
         <v>40004.0</v>
@@ -10421,7 +10569,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>12</v>
@@ -10441,13 +10589,13 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>14</v>
@@ -10461,7 +10609,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>12</v>
@@ -10481,7 +10629,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>12</v>
@@ -10492,7 +10640,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>19</v>
@@ -10512,13 +10660,13 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>14</v>
@@ -10532,7 +10680,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>19</v>
@@ -10552,7 +10700,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>19</v>
@@ -10572,7 +10720,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>19</v>
@@ -10583,7 +10731,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>28</v>
@@ -10603,13 +10751,13 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>14</v>
@@ -10623,7 +10771,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>28</v>
@@ -10643,7 +10791,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>28</v>
@@ -10654,10 +10802,10 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>13</v>
@@ -10674,13 +10822,13 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>14</v>
@@ -10694,10 +10842,10 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>17</v>
@@ -10714,10 +10862,10 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>23</v>
@@ -10726,7 +10874,7 @@
         <v>24</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>21</v>
@@ -10734,10 +10882,10 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H103" s="3">
         <v>43288.0</v>
@@ -10745,10 +10893,10 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>13</v>
@@ -10765,13 +10913,13 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>14</v>
@@ -10785,10 +10933,10 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>17</v>
@@ -10805,10 +10953,10 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H107" s="3">
         <v>42264.0</v>
@@ -10816,24 +10964,24 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>23</v>
@@ -10850,10 +10998,10 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H110" s="3">
         <v>41828.0</v>

--- a/google_data/Pobočky/Výroba/Databaze Výroba 2026.xlsx
+++ b/google_data/Pobočky/Výroba/Databaze Výroba 2026.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2681" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2731" uniqueCount="215">
   <si>
     <t>Datum</t>
   </si>
@@ -121,6 +121,30 @@
     <t>Pátek</t>
   </si>
   <si>
+    <t>06.06.2026</t>
+  </si>
+  <si>
+    <t>Sobota</t>
+  </si>
+  <si>
+    <t>07.06.2026</t>
+  </si>
+  <si>
+    <t>Neděle</t>
+  </si>
+  <si>
+    <t>08.06.2026</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>09.06.2026</t>
+  </si>
+  <si>
     <t>01.05.2026</t>
   </si>
   <si>
@@ -130,15 +154,9 @@
     <t>02.05.2026</t>
   </si>
   <si>
-    <t>Sobota</t>
-  </si>
-  <si>
     <t>03.05.2026</t>
   </si>
   <si>
-    <t>Neděle</t>
-  </si>
-  <si>
     <t>04.05.2026</t>
   </si>
   <si>
@@ -152,12 +170,6 @@
   </si>
   <si>
     <t>08.05.2026</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>09:00</t>
   </si>
   <si>
     <t>09.05.2026</t>
@@ -1338,6 +1350,190 @@
         <v>40484.25</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" s="3">
+        <v>40244.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H24" s="3">
+        <v>40004.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" s="3">
+        <v>40512.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" s="3">
+        <v>40504.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1387,7 +1583,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>33</v>
@@ -1407,13 +1603,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -1427,7 +1623,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>33</v>
@@ -1447,7 +1643,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>33</v>
@@ -1458,10 +1654,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>23</v>
@@ -1478,10 +1674,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H7" s="3">
         <v>40004.0</v>
@@ -1489,10 +1685,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H8" s="3">
         <v>40004.0</v>
@@ -1500,7 +1696,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -1520,13 +1716,13 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -1540,7 +1736,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>12</v>
@@ -1560,7 +1756,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>12</v>
@@ -1571,13 +1767,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>14</v>
@@ -1591,7 +1787,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>19</v>
@@ -1611,7 +1807,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>19</v>
@@ -1631,7 +1827,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>19</v>
@@ -1642,7 +1838,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>28</v>
@@ -1662,13 +1858,13 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>14</v>
@@ -1682,7 +1878,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>28</v>
@@ -1693,7 +1889,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>30</v>
@@ -1713,13 +1909,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>14</v>
@@ -1733,7 +1929,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>30</v>
@@ -1753,7 +1949,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>30</v>
@@ -1773,7 +1969,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>30</v>
@@ -1784,27 +1980,27 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>33</v>
@@ -1816,15 +2012,15 @@
         <v>14</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>33</v>
@@ -1835,31 +2031,31 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H29" s="3"/>
       <c r="P29" s="3">
@@ -1890,7 +2086,7 @@
         <v>0.0</v>
       </c>
       <c r="AD29" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="AI29" s="3">
         <v>0.0</v>
@@ -1937,10 +2133,10 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H30" s="3">
         <v>40004.0</v>
@@ -1948,13 +2144,13 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>14</v>
@@ -1968,7 +2164,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -1988,7 +2184,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>12</v>
@@ -1999,27 +2195,27 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>19</v>
@@ -2031,15 +2227,15 @@
         <v>14</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>19</v>
@@ -2059,7 +2255,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>19</v>
@@ -2070,13 +2266,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>14</v>
@@ -2090,7 +2286,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>28</v>
@@ -2110,7 +2306,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>28</v>
@@ -2121,13 +2317,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>14</v>
@@ -2141,7 +2337,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>30</v>
@@ -2161,7 +2357,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>30</v>
@@ -2181,7 +2377,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>30</v>
@@ -2192,13 +2388,13 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>14</v>
@@ -2212,7 +2408,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>33</v>
@@ -2232,7 +2428,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>33</v>
@@ -2243,10 +2439,10 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H48" s="3">
         <v>40004.0</v>
@@ -2254,10 +2450,10 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H49" s="3">
         <v>40004.0</v>
@@ -2265,7 +2461,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>12</v>
@@ -2285,13 +2481,13 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>14</v>
@@ -2305,7 +2501,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>12</v>
@@ -2316,7 +2512,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>19</v>
@@ -2336,13 +2532,13 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>14</v>
@@ -2356,7 +2552,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>19</v>
@@ -2376,7 +2572,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>19</v>
@@ -2396,7 +2592,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>19</v>
@@ -2407,13 +2603,13 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>14</v>
@@ -2427,7 +2623,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>28</v>
@@ -2447,7 +2643,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>28</v>
@@ -2467,7 +2663,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>28</v>
@@ -2478,13 +2674,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>14</v>
@@ -2498,7 +2694,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>30</v>
@@ -2518,7 +2714,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>30</v>
@@ -2538,7 +2734,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>30</v>
@@ -2558,7 +2754,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>30</v>
@@ -2569,7 +2765,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>33</v>
@@ -2589,13 +2785,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>14</v>
@@ -2609,7 +2805,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>33</v>
@@ -2629,7 +2825,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>33</v>
@@ -2640,10 +2836,10 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>23</v>
@@ -2660,10 +2856,10 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H72" s="3">
         <v>40928.0</v>
@@ -2671,10 +2867,10 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H73" s="3">
         <v>40004.0</v>
@@ -2682,7 +2878,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>12</v>
@@ -2702,7 +2898,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>12</v>
@@ -2722,7 +2918,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>12</v>
@@ -2733,7 +2929,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>19</v>
@@ -2753,7 +2949,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>19</v>
@@ -2773,7 +2969,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>19</v>
@@ -2793,7 +2989,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>19</v>
@@ -2804,7 +3000,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>28</v>
@@ -2824,7 +3020,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>28</v>
@@ -2844,7 +3040,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>28</v>
@@ -2855,7 +3051,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>30</v>
@@ -2875,7 +3071,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>30</v>
@@ -2895,7 +3091,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>30</v>
@@ -2915,7 +3111,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>30</v>
@@ -2926,7 +3122,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>33</v>
@@ -2946,7 +3142,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>33</v>
@@ -2966,7 +3162,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>33</v>
@@ -2977,10 +3173,10 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>23</v>
@@ -2997,10 +3193,10 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H92" s="3">
         <v>41564.0</v>
@@ -3008,10 +3204,10 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H93" s="3">
         <v>40004.0</v>
@@ -3066,7 +3262,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>28</v>
@@ -3086,13 +3282,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -3106,7 +3302,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>28</v>
@@ -3126,7 +3322,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>28</v>
@@ -3137,7 +3333,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>30</v>
@@ -3157,13 +3353,13 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>14</v>
@@ -3177,7 +3373,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>30</v>
@@ -3197,7 +3393,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>30</v>
@@ -3217,7 +3413,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>30</v>
@@ -3228,7 +3424,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>33</v>
@@ -3248,13 +3444,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -3268,7 +3464,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>33</v>
@@ -3288,7 +3484,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>33</v>
@@ -3299,10 +3495,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>23</v>
@@ -3319,10 +3515,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H16" s="3">
         <v>40100.0</v>
@@ -3330,10 +3526,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H17" s="3">
         <v>40004.0</v>
@@ -3341,7 +3537,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>12</v>
@@ -3361,13 +3557,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>14</v>
@@ -3381,7 +3577,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>12</v>
@@ -3401,7 +3597,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>12</v>
@@ -3412,7 +3608,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>19</v>
@@ -3432,13 +3628,13 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>14</v>
@@ -3452,7 +3648,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>19</v>
@@ -3472,13 +3668,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>24</v>
@@ -3487,12 +3683,12 @@
         <v>15</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>19</v>
@@ -3507,12 +3703,12 @@
         <v>25</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>19</v>
@@ -3523,7 +3719,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>28</v>
@@ -3543,13 +3739,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>14</v>
@@ -3563,7 +3759,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>28</v>
@@ -3583,7 +3779,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>28</v>
@@ -3594,7 +3790,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>30</v>
@@ -3614,13 +3810,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>14</v>
@@ -3634,7 +3830,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>30</v>
@@ -3654,7 +3850,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>30</v>
@@ -3674,7 +3870,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>30</v>
@@ -3685,7 +3881,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>33</v>
@@ -3697,35 +3893,35 @@
         <v>14</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>33</v>
@@ -3737,15 +3933,15 @@
         <v>14</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>33</v>
@@ -3756,10 +3952,10 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>23</v>
@@ -3776,10 +3972,10 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H42" s="3">
         <v>40502.0</v>
@@ -3787,10 +3983,10 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H43" s="3">
         <v>40004.0</v>
@@ -3798,7 +3994,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>12</v>
@@ -3810,15 +4006,15 @@
         <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>12</v>
@@ -3830,15 +4026,15 @@
         <v>14</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>12</v>
@@ -3849,7 +4045,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>19</v>
@@ -3869,7 +4065,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>19</v>
@@ -3889,19 +4085,19 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>14</v>
@@ -3909,7 +4105,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>19</v>
@@ -3918,10 +4114,10 @@
         <v>23</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>14</v>
@@ -3929,7 +4125,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>19</v>
@@ -3940,13 +4136,13 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>14</v>
@@ -3960,7 +4156,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>28</v>
@@ -3980,7 +4176,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>28</v>
@@ -4000,7 +4196,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>28</v>
@@ -4011,7 +4207,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>30</v>
@@ -4031,13 +4227,13 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>14</v>
@@ -4051,7 +4247,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>30</v>
@@ -4071,7 +4267,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>30</v>
@@ -4091,7 +4287,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>30</v>
@@ -4102,7 +4298,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>33</v>
@@ -4122,13 +4318,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>14</v>
@@ -4142,7 +4338,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>33</v>
@@ -4153,10 +4349,10 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>23</v>
@@ -4173,10 +4369,10 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H65" s="3">
         <v>40970.0</v>
@@ -4184,10 +4380,10 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H66" s="3">
         <v>40004.0</v>
@@ -4195,7 +4391,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>12</v>
@@ -4215,13 +4411,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>14</v>
@@ -4235,7 +4431,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>12</v>
@@ -4246,7 +4442,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>19</v>
@@ -4266,13 +4462,13 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>14</v>
@@ -4286,19 +4482,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>14</v>
@@ -4306,7 +4502,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>19</v>
@@ -4315,18 +4511,18 @@
         <v>23</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>19</v>
@@ -4337,7 +4533,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>28</v>
@@ -4357,13 +4553,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>14</v>
@@ -4377,7 +4573,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>28</v>
@@ -4388,7 +4584,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>30</v>
@@ -4408,13 +4604,13 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>14</v>
@@ -4428,7 +4624,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>30</v>
@@ -4448,7 +4644,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>30</v>
@@ -4459,7 +4655,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>33</v>
@@ -4479,13 +4675,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>14</v>
@@ -4499,7 +4695,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>33</v>
@@ -4510,10 +4706,10 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>23</v>
@@ -4530,10 +4726,10 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H86" s="3">
         <v>41270.0</v>
@@ -4541,10 +4737,10 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H87" s="3">
         <v>40004.0</v>
@@ -4552,7 +4748,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>12</v>
@@ -4572,13 +4768,13 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>14</v>
@@ -4592,7 +4788,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>12</v>
@@ -4603,7 +4799,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>19</v>
@@ -4623,7 +4819,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>19</v>
@@ -4643,27 +4839,27 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>19</v>
@@ -4672,18 +4868,18 @@
         <v>23</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>19</v>
@@ -4694,7 +4890,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>28</v>
@@ -4714,13 +4910,13 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>14</v>
@@ -4734,7 +4930,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>28</v>
@@ -4745,7 +4941,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>30</v>
@@ -4765,13 +4961,13 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>14</v>
@@ -4785,7 +4981,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>30</v>
@@ -4805,7 +5001,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>30</v>
@@ -4825,7 +5021,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>30</v>
@@ -4883,24 +5079,24 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H3" s="3">
         <v>40004.0</v>
@@ -4908,7 +5104,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -4928,13 +5124,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
@@ -4948,7 +5144,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
@@ -4968,7 +5164,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -4979,7 +5175,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
@@ -4999,13 +5195,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>14</v>
@@ -5019,7 +5215,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>19</v>
@@ -5031,15 +5227,15 @@
         <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>19</v>
@@ -5059,7 +5255,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>19</v>
@@ -5070,7 +5266,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>28</v>
@@ -5090,13 +5286,13 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
@@ -5110,7 +5306,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>28</v>
@@ -5130,7 +5326,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>28</v>
@@ -5141,7 +5337,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>30</v>
@@ -5161,27 +5357,27 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
@@ -5193,15 +5389,15 @@
         <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>30</v>
@@ -5221,7 +5417,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>30</v>
@@ -5234,12 +5430,12 @@
         <v>40483.5</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>30</v>
@@ -5276,7 +5472,7 @@
         <v>0.0</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="AI22" s="3">
         <v>0.0</v>
@@ -5323,7 +5519,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>33</v>
@@ -5343,13 +5539,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>14</v>
@@ -5363,7 +5559,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>33</v>
@@ -5383,7 +5579,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>33</v>
@@ -5394,10 +5590,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>23</v>
@@ -5414,24 +5610,24 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H29" s="3">
         <v>40400.0</v>
@@ -5439,24 +5635,24 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H31" s="3">
         <v>40004.0</v>
@@ -5464,7 +5660,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -5484,13 +5680,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>14</v>
@@ -5504,7 +5700,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>12</v>
@@ -5524,7 +5720,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>12</v>
@@ -5535,7 +5731,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>19</v>
@@ -5555,27 +5751,27 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>19</v>
@@ -5595,7 +5791,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>19</v>
@@ -5615,7 +5811,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>19</v>
@@ -5628,12 +5824,12 @@
         <v>41160.0</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>19</v>
@@ -5670,7 +5866,7 @@
         <v>0.0</v>
       </c>
       <c r="AD41" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="AI41" s="3">
         <v>0.0</v>
@@ -5717,7 +5913,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>28</v>
@@ -5737,13 +5933,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>14</v>
@@ -5757,7 +5953,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>28</v>
@@ -5777,7 +5973,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>28</v>
@@ -5788,7 +5984,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>30</v>
@@ -5808,27 +6004,27 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>30</v>
@@ -5840,15 +6036,15 @@
         <v>14</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>30</v>
@@ -5868,7 +6064,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>30</v>
@@ -5881,12 +6077,12 @@
         <v>41286.0</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>30</v>
@@ -5923,7 +6119,7 @@
         <v>0.0</v>
       </c>
       <c r="AD51" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="AI51" s="3">
         <v>0.0</v>
@@ -5970,7 +6166,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>33</v>
@@ -5990,13 +6186,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>14</v>
@@ -6010,7 +6206,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>33</v>
@@ -6030,7 +6226,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>33</v>
@@ -6041,10 +6237,10 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>23</v>
@@ -6061,24 +6257,24 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H58" s="3">
         <v>40784.0</v>
@@ -6086,24 +6282,24 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H60" s="3">
         <v>40004.0</v>
@@ -6111,7 +6307,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>12</v>
@@ -6131,13 +6327,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>14</v>
@@ -6151,7 +6347,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>12</v>
@@ -6171,7 +6367,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>12</v>
@@ -6182,7 +6378,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>19</v>
@@ -6202,13 +6398,13 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>14</v>
@@ -6222,7 +6418,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>19</v>
@@ -6242,7 +6438,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>19</v>
@@ -6262,7 +6458,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>19</v>
@@ -6273,7 +6469,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>28</v>
@@ -6293,27 +6489,27 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>28</v>
@@ -6325,15 +6521,15 @@
         <v>14</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>28</v>
@@ -6346,12 +6542,12 @@
         <v>41264.0</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>28</v>
@@ -6388,7 +6584,7 @@
         <v>0.0</v>
       </c>
       <c r="AD74" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="AI74" s="3">
         <v>0.0</v>
@@ -6435,7 +6631,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>30</v>
@@ -6455,13 +6651,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>14</v>
@@ -6475,7 +6671,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>30</v>
@@ -6495,7 +6691,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>30</v>
@@ -6506,7 +6702,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>33</v>
@@ -6526,13 +6722,13 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>14</v>
@@ -6546,7 +6742,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>33</v>
@@ -6566,7 +6762,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>33</v>
@@ -6577,10 +6773,10 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>23</v>
@@ -6597,24 +6793,24 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H85" s="3">
         <v>41324.0</v>
@@ -6622,24 +6818,24 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H87" s="3">
         <v>40004.0</v>
@@ -6647,7 +6843,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>12</v>
@@ -6667,13 +6863,13 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>14</v>
@@ -6687,7 +6883,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>12</v>
@@ -6698,7 +6894,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>19</v>
@@ -6718,21 +6914,21 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>19</v>
@@ -6752,7 +6948,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>19</v>
@@ -6772,7 +6968,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>19</v>
@@ -6783,7 +6979,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>28</v>
@@ -6803,13 +6999,13 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>14</v>
@@ -6823,7 +7019,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>28</v>
@@ -6843,7 +7039,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>28</v>
@@ -6854,7 +7050,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>30</v>
@@ -6874,13 +7070,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>14</v>
@@ -6894,7 +7090,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>30</v>
@@ -6914,7 +7110,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>30</v>
@@ -6934,7 +7130,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>30</v>
@@ -6945,7 +7141,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>33</v>
@@ -6965,13 +7161,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>14</v>
@@ -6985,7 +7181,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>33</v>
@@ -7005,7 +7201,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>33</v>
@@ -7016,10 +7212,10 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>23</v>
@@ -7036,24 +7232,24 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H111" s="3">
         <v>41708.0</v>
@@ -7061,24 +7257,24 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H113" s="3">
         <v>40004.0</v>
@@ -7086,7 +7282,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>12</v>
@@ -7106,13 +7302,13 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>14</v>
@@ -7126,7 +7322,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>12</v>
@@ -7146,7 +7342,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>12</v>
@@ -7157,7 +7353,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>19</v>
@@ -7177,13 +7373,13 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>14</v>
@@ -7197,7 +7393,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>19</v>
@@ -7217,19 +7413,19 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>14</v>
@@ -7237,7 +7433,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>19</v>
@@ -7246,7 +7442,7 @@
         <v>23</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>25</v>
@@ -7257,7 +7453,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>19</v>
@@ -7315,24 +7511,24 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H3" s="3">
         <v>40004.0</v>
@@ -7340,7 +7536,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -7360,13 +7556,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
@@ -7380,7 +7576,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
@@ -7400,7 +7596,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -7411,7 +7607,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
@@ -7423,35 +7619,35 @@
         <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>19</v>
@@ -7463,15 +7659,15 @@
         <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>19</v>
@@ -7491,7 +7687,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>19</v>
@@ -7502,7 +7698,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>28</v>
@@ -7514,35 +7710,35 @@
         <v>14</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>28</v>
@@ -7553,7 +7749,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>30</v>
@@ -7565,35 +7761,35 @@
         <v>14</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>30</v>
@@ -7613,7 +7809,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
@@ -7624,7 +7820,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>33</v>
@@ -7644,13 +7840,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>14</v>
@@ -7664,7 +7860,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>33</v>
@@ -7684,7 +7880,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>33</v>
@@ -7695,10 +7891,10 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>23</v>
@@ -7715,24 +7911,24 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H26" s="3">
         <v>40400.0</v>
@@ -7740,24 +7936,24 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H28" s="3">
         <v>40004.0</v>
@@ -7765,7 +7961,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>12</v>
@@ -7785,13 +7981,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>14</v>
@@ -7805,7 +8001,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>12</v>
@@ -7825,7 +8021,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -7836,7 +8032,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>19</v>
@@ -7848,35 +8044,35 @@
         <v>14</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>19</v>
@@ -7888,15 +8084,15 @@
         <v>14</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>19</v>
@@ -7916,7 +8112,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>19</v>
@@ -7927,7 +8123,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>28</v>
@@ -7947,13 +8143,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>14</v>
@@ -7967,7 +8163,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>28</v>
@@ -7987,7 +8183,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>28</v>
@@ -7998,7 +8194,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>30</v>
@@ -8010,35 +8206,35 @@
         <v>14</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>30</v>
@@ -8050,15 +8246,15 @@
         <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>30</v>
@@ -8078,7 +8274,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>30</v>
@@ -8089,7 +8285,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>33</v>
@@ -8101,35 +8297,35 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>33</v>
@@ -8140,10 +8336,10 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>23</v>
@@ -8160,24 +8356,24 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H52" s="3">
         <v>40784.0</v>
@@ -8185,24 +8381,24 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H54" s="3">
         <v>40004.0</v>
@@ -8210,7 +8406,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>12</v>
@@ -8222,35 +8418,35 @@
         <v>14</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>12</v>
@@ -8262,15 +8458,15 @@
         <v>14</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>12</v>
@@ -8281,7 +8477,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>19</v>
@@ -8301,13 +8497,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>14</v>
@@ -8321,7 +8517,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>19</v>
@@ -8341,7 +8537,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>19</v>
@@ -8350,18 +8546,18 @@
         <v>23</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>19</v>
@@ -8372,7 +8568,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>28</v>
@@ -8392,13 +8588,13 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>14</v>
@@ -8412,7 +8608,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>28</v>
@@ -8432,7 +8628,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>28</v>
@@ -8443,7 +8639,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>30</v>
@@ -8455,35 +8651,35 @@
         <v>14</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>30</v>
@@ -8495,15 +8691,15 @@
         <v>14</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>30</v>
@@ -8523,7 +8719,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>30</v>
@@ -8534,7 +8730,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>33</v>
@@ -8554,13 +8750,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>14</v>
@@ -8574,7 +8770,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>33</v>
@@ -8594,7 +8790,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>33</v>
@@ -8605,10 +8801,10 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>23</v>
@@ -8625,24 +8821,24 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H79" s="3">
         <v>41312.0</v>
@@ -8650,24 +8846,24 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H81" s="3">
         <v>40004.0</v>
@@ -8675,7 +8871,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>12</v>
@@ -8695,13 +8891,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>14</v>
@@ -8715,7 +8911,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>12</v>
@@ -8735,7 +8931,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>12</v>
@@ -8746,7 +8942,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>19</v>
@@ -8766,13 +8962,13 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>14</v>
@@ -8786,7 +8982,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>19</v>
@@ -8806,7 +9002,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>19</v>
@@ -8826,7 +9022,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>19</v>
@@ -8837,7 +9033,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>28</v>
@@ -8857,13 +9053,13 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>14</v>
@@ -8877,7 +9073,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>28</v>
@@ -8897,7 +9093,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>28</v>
@@ -8908,7 +9104,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>30</v>
@@ -8920,29 +9116,29 @@
         <v>14</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>30</v>
@@ -8954,15 +9150,15 @@
         <v>14</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>30</v>
@@ -8982,7 +9178,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>30</v>
@@ -8993,7 +9189,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>33</v>
@@ -9013,13 +9209,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>14</v>
@@ -9033,7 +9229,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>33</v>
@@ -9053,7 +9249,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>33</v>
@@ -9064,24 +9260,24 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>23</v>
@@ -9098,10 +9294,10 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H106" s="3">
         <v>41696.0</v>
@@ -9156,7 +9352,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>30</v>
@@ -9165,12 +9361,12 @@
         <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>30</v>
@@ -9181,27 +9377,27 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>33</v>
@@ -9213,35 +9409,35 @@
         <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>33</v>
@@ -9252,10 +9448,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>23</v>
@@ -9272,24 +9468,24 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H10" s="3">
         <v>40004.0</v>
@@ -9297,24 +9493,24 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H12" s="3">
         <v>40004.0</v>
@@ -9322,7 +9518,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
@@ -9342,7 +9538,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
@@ -9362,13 +9558,13 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>14</v>
@@ -9382,7 +9578,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>12</v>
@@ -9393,7 +9589,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>19</v>
@@ -9413,7 +9609,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>19</v>
@@ -9433,13 +9629,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>14</v>
@@ -9453,7 +9649,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>19</v>
@@ -9473,7 +9669,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>19</v>
@@ -9484,7 +9680,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>28</v>
@@ -9504,7 +9700,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>28</v>
@@ -9524,13 +9720,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>14</v>
@@ -9544,7 +9740,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>28</v>
@@ -9555,7 +9751,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>30</v>
@@ -9575,7 +9771,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>30</v>
@@ -9595,13 +9791,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>14</v>
@@ -9615,7 +9811,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>30</v>
@@ -9627,15 +9823,15 @@
         <v>24</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>30</v>
@@ -9646,7 +9842,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>33</v>
@@ -9666,13 +9862,13 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>14</v>
@@ -9686,7 +9882,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>33</v>
@@ -9706,7 +9902,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>33</v>
@@ -9717,10 +9913,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>23</v>
@@ -9737,24 +9933,24 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H37" s="3">
         <v>40532.0</v>
@@ -9762,24 +9958,24 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H39" s="3">
         <v>40004.0</v>
@@ -9787,7 +9983,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>12</v>
@@ -9807,13 +10003,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>14</v>
@@ -9827,7 +10023,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>12</v>
@@ -9838,7 +10034,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>19</v>
@@ -9850,35 +10046,35 @@
         <v>14</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>19</v>
@@ -9898,7 +10094,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>19</v>
@@ -9909,7 +10105,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>28</v>
@@ -9921,35 +10117,35 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>28</v>
@@ -9960,7 +10156,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>30</v>
@@ -9972,35 +10168,35 @@
         <v>14</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>30</v>
@@ -10015,12 +10211,12 @@
         <v>24</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>30</v>
@@ -10032,15 +10228,15 @@
         <v>24</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>30</v>
@@ -10051,7 +10247,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>33</v>
@@ -10071,13 +10267,13 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>14</v>
@@ -10091,7 +10287,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>33</v>
@@ -10111,7 +10307,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>33</v>
@@ -10122,10 +10318,10 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>23</v>
@@ -10142,24 +10338,24 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H61" s="3">
         <v>40904.0</v>
@@ -10167,24 +10363,24 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H63" s="3">
         <v>40004.0</v>
@@ -10192,7 +10388,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>12</v>
@@ -10212,13 +10408,13 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>14</v>
@@ -10232,7 +10428,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>12</v>
@@ -10243,7 +10439,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>19</v>
@@ -10263,13 +10459,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>14</v>
@@ -10283,7 +10479,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>19</v>
@@ -10303,7 +10499,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>19</v>
@@ -10323,7 +10519,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>19</v>
@@ -10334,7 +10530,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>28</v>
@@ -10346,35 +10542,35 @@
         <v>14</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>28</v>
@@ -10389,12 +10585,12 @@
         <v>21</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>28</v>
@@ -10405,7 +10601,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>30</v>
@@ -10425,13 +10621,13 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>14</v>
@@ -10445,7 +10641,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>30</v>
@@ -10465,7 +10661,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>30</v>
@@ -10476,7 +10672,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>33</v>
@@ -10488,35 +10684,35 @@
         <v>14</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>33</v>
@@ -10527,10 +10723,10 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>23</v>
@@ -10547,10 +10743,10 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H84" s="3">
         <v>41444.0</v>
@@ -10558,10 +10754,10 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H85" s="3">
         <v>40004.0</v>
@@ -10569,7 +10765,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>12</v>
@@ -10589,13 +10785,13 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>14</v>
@@ -10609,7 +10805,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>12</v>
@@ -10629,7 +10825,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>12</v>
@@ -10640,7 +10836,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>19</v>
@@ -10660,13 +10856,13 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>14</v>
@@ -10680,7 +10876,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>19</v>
@@ -10700,7 +10896,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>19</v>
@@ -10720,7 +10916,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>19</v>
@@ -10731,7 +10927,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>28</v>
@@ -10751,13 +10947,13 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>14</v>
@@ -10771,7 +10967,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>28</v>
@@ -10791,7 +10987,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>28</v>
@@ -10802,7 +10998,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>30</v>
@@ -10822,13 +11018,13 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>14</v>
@@ -10842,7 +11038,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>30</v>
@@ -10862,7 +11058,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>30</v>
@@ -10882,7 +11078,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>30</v>
@@ -10893,7 +11089,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>33</v>
@@ -10913,13 +11109,13 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>14</v>
@@ -10933,7 +11129,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>33</v>
@@ -10953,7 +11149,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>33</v>
@@ -10964,24 +11160,24 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>23</v>
@@ -10998,10 +11194,10 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H110" s="3">
         <v>41828.0</v>

--- a/google_data/Pobočky/Výroba/Databaze Výroba 2026.xlsx
+++ b/google_data/Pobočky/Výroba/Databaze Výroba 2026.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2731" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2827" uniqueCount="222">
   <si>
     <t>Datum</t>
   </si>
@@ -145,6 +145,42 @@
     <t>09.06.2026</t>
   </si>
   <si>
+    <t>10.06.2026</t>
+  </si>
+  <si>
+    <t>11.06.2026</t>
+  </si>
+  <si>
+    <t>12.06.2026</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>13.06.2026</t>
+  </si>
+  <si>
+    <t>Lažek Jaroslav</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>14.06.2026</t>
+  </si>
+  <si>
+    <t>15.06.2026</t>
+  </si>
+  <si>
     <t>01.05.2026</t>
   </si>
   <si>
@@ -175,12 +211,6 @@
     <t>09.05.2026</t>
   </si>
   <si>
-    <t>Lažek Jaroslav</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
     <t>Zadej tržbu</t>
   </si>
   <si>
@@ -304,9 +334,6 @@
     <t>14.04.2026</t>
   </si>
   <si>
-    <t>11:00</t>
-  </si>
-  <si>
     <t>17:00</t>
   </si>
   <si>
@@ -560,12 +587,6 @@
   </si>
   <si>
     <t>02.01.2026</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>09:30</t>
   </si>
   <si>
     <t xml:space="preserve">Paziak Viktoriia </t>
@@ -1534,6 +1555,352 @@
         <v>40504.0</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H36" s="3">
+        <v>40456.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H40" s="3">
+        <v>40988.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H44" s="3">
+        <v>41324.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H47" s="3">
+        <v>41125.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H48" s="3">
+        <v>40004.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H52" s="3">
+        <v>41614.75</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1583,7 +1950,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>33</v>
@@ -1603,13 +1970,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -1623,7 +1990,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>33</v>
@@ -1643,7 +2010,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>33</v>
@@ -1654,7 +2021,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>35</v>
@@ -1674,7 +2041,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>35</v>
@@ -1685,7 +2052,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>37</v>
@@ -1696,7 +2063,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -1716,13 +2083,13 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -1736,7 +2103,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>12</v>
@@ -1756,7 +2123,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>12</v>
@@ -1767,13 +2134,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>14</v>
@@ -1787,7 +2154,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>19</v>
@@ -1807,7 +2174,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>19</v>
@@ -1827,7 +2194,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>19</v>
@@ -1838,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>28</v>
@@ -1858,13 +2225,13 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>14</v>
@@ -1878,7 +2245,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>28</v>
@@ -1889,7 +2256,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>30</v>
@@ -1909,13 +2276,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>14</v>
@@ -1929,7 +2296,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>30</v>
@@ -1949,7 +2316,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>30</v>
@@ -1969,7 +2336,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>30</v>
@@ -1980,13 +2347,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>14</v>
@@ -2000,7 +2367,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>33</v>
@@ -2020,7 +2387,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>33</v>
@@ -2031,13 +2398,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>40</v>
@@ -2046,13 +2413,13 @@
         <v>25</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>35</v>
@@ -2086,7 +2453,7 @@
         <v>0.0</v>
       </c>
       <c r="AD29" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="AI29" s="3">
         <v>0.0</v>
@@ -2133,7 +2500,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>37</v>
@@ -2144,13 +2511,13 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>14</v>
@@ -2164,7 +2531,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -2184,7 +2551,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>12</v>
@@ -2195,27 +2562,27 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>19</v>
@@ -2227,15 +2594,15 @@
         <v>14</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>19</v>
@@ -2255,7 +2622,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>19</v>
@@ -2266,13 +2633,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>14</v>
@@ -2286,7 +2653,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>28</v>
@@ -2306,7 +2673,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>28</v>
@@ -2317,13 +2684,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>14</v>
@@ -2337,7 +2704,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>30</v>
@@ -2357,7 +2724,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>30</v>
@@ -2377,7 +2744,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>30</v>
@@ -2388,13 +2755,13 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>14</v>
@@ -2408,7 +2775,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>33</v>
@@ -2428,7 +2795,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>33</v>
@@ -2439,7 +2806,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>35</v>
@@ -2450,7 +2817,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>37</v>
@@ -2461,7 +2828,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>12</v>
@@ -2481,13 +2848,13 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>14</v>
@@ -2501,7 +2868,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>12</v>
@@ -2512,7 +2879,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>19</v>
@@ -2532,13 +2899,13 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>14</v>
@@ -2552,7 +2919,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>19</v>
@@ -2572,7 +2939,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>19</v>
@@ -2592,7 +2959,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>19</v>
@@ -2603,13 +2970,13 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>14</v>
@@ -2623,7 +2990,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>28</v>
@@ -2643,7 +3010,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>28</v>
@@ -2663,7 +3030,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>28</v>
@@ -2674,13 +3041,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>14</v>
@@ -2694,7 +3061,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>30</v>
@@ -2714,7 +3081,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>30</v>
@@ -2734,7 +3101,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>30</v>
@@ -2754,7 +3121,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>30</v>
@@ -2765,7 +3132,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>33</v>
@@ -2785,13 +3152,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>14</v>
@@ -2805,7 +3172,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>33</v>
@@ -2825,7 +3192,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>33</v>
@@ -2836,7 +3203,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>35</v>
@@ -2856,7 +3223,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>35</v>
@@ -2867,7 +3234,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>37</v>
@@ -2878,7 +3245,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>12</v>
@@ -2898,7 +3265,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>12</v>
@@ -2918,7 +3285,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>12</v>
@@ -2929,7 +3296,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>19</v>
@@ -2949,7 +3316,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>19</v>
@@ -2969,7 +3336,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>19</v>
@@ -2989,7 +3356,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>19</v>
@@ -3000,7 +3367,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>28</v>
@@ -3020,7 +3387,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>28</v>
@@ -3040,7 +3407,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>28</v>
@@ -3051,7 +3418,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>30</v>
@@ -3071,7 +3438,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>30</v>
@@ -3091,7 +3458,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>30</v>
@@ -3111,7 +3478,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>30</v>
@@ -3122,7 +3489,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>33</v>
@@ -3142,7 +3509,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>33</v>
@@ -3162,7 +3529,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>33</v>
@@ -3173,7 +3540,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>35</v>
@@ -3193,7 +3560,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>35</v>
@@ -3204,7 +3571,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>37</v>
@@ -3262,7 +3629,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>28</v>
@@ -3282,13 +3649,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -3302,7 +3669,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>28</v>
@@ -3322,7 +3689,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>28</v>
@@ -3333,7 +3700,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>30</v>
@@ -3353,13 +3720,13 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>14</v>
@@ -3373,7 +3740,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>30</v>
@@ -3393,7 +3760,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>30</v>
@@ -3413,7 +3780,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>30</v>
@@ -3424,7 +3791,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>33</v>
@@ -3444,13 +3811,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -3464,7 +3831,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>33</v>
@@ -3484,7 +3851,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>33</v>
@@ -3495,7 +3862,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>35</v>
@@ -3515,7 +3882,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>35</v>
@@ -3526,7 +3893,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>37</v>
@@ -3537,7 +3904,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>12</v>
@@ -3557,13 +3924,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>14</v>
@@ -3577,7 +3944,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>12</v>
@@ -3597,7 +3964,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>12</v>
@@ -3608,7 +3975,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>19</v>
@@ -3628,13 +3995,13 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>14</v>
@@ -3648,7 +4015,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>19</v>
@@ -3668,13 +4035,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>24</v>
@@ -3683,12 +4050,12 @@
         <v>15</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>19</v>
@@ -3703,12 +4070,12 @@
         <v>25</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>19</v>
@@ -3719,7 +4086,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>28</v>
@@ -3739,13 +4106,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>14</v>
@@ -3759,7 +4126,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>28</v>
@@ -3779,7 +4146,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>28</v>
@@ -3790,7 +4157,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>30</v>
@@ -3810,13 +4177,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>14</v>
@@ -3830,7 +4197,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>30</v>
@@ -3850,7 +4217,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>30</v>
@@ -3870,7 +4237,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>30</v>
@@ -3881,7 +4248,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>33</v>
@@ -3893,35 +4260,35 @@
         <v>14</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>33</v>
@@ -3933,15 +4300,15 @@
         <v>14</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>33</v>
@@ -3952,7 +4319,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>35</v>
@@ -3972,7 +4339,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>35</v>
@@ -3983,7 +4350,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>37</v>
@@ -3994,7 +4361,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>12</v>
@@ -4014,7 +4381,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>12</v>
@@ -4034,7 +4401,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>12</v>
@@ -4045,7 +4412,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>19</v>
@@ -4065,7 +4432,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>19</v>
@@ -4085,19 +4452,19 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>14</v>
@@ -4105,7 +4472,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>19</v>
@@ -4114,10 +4481,10 @@
         <v>23</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>14</v>
@@ -4125,7 +4492,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>19</v>
@@ -4136,13 +4503,13 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>14</v>
@@ -4156,7 +4523,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>28</v>
@@ -4176,7 +4543,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>28</v>
@@ -4196,7 +4563,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>28</v>
@@ -4207,7 +4574,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>30</v>
@@ -4227,13 +4594,13 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>14</v>
@@ -4247,7 +4614,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>30</v>
@@ -4267,7 +4634,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>30</v>
@@ -4287,7 +4654,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>30</v>
@@ -4298,7 +4665,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>33</v>
@@ -4318,13 +4685,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>14</v>
@@ -4338,7 +4705,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>33</v>
@@ -4349,7 +4716,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>35</v>
@@ -4369,7 +4736,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>35</v>
@@ -4380,7 +4747,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>37</v>
@@ -4391,7 +4758,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>12</v>
@@ -4411,13 +4778,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>14</v>
@@ -4431,7 +4798,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>12</v>
@@ -4442,7 +4809,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>19</v>
@@ -4462,13 +4829,13 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>14</v>
@@ -4482,19 +4849,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>14</v>
@@ -4502,7 +4869,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>19</v>
@@ -4511,18 +4878,18 @@
         <v>23</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>19</v>
@@ -4533,7 +4900,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>28</v>
@@ -4553,13 +4920,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>14</v>
@@ -4573,7 +4940,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>28</v>
@@ -4584,7 +4951,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>30</v>
@@ -4604,13 +4971,13 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>14</v>
@@ -4624,7 +4991,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>30</v>
@@ -4644,7 +5011,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>30</v>
@@ -4655,7 +5022,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>33</v>
@@ -4675,13 +5042,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>14</v>
@@ -4695,7 +5062,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>33</v>
@@ -4706,7 +5073,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>35</v>
@@ -4726,7 +5093,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>35</v>
@@ -4737,7 +5104,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>37</v>
@@ -4748,7 +5115,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>12</v>
@@ -4768,13 +5135,13 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>14</v>
@@ -4788,7 +5155,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>12</v>
@@ -4799,7 +5166,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>19</v>
@@ -4819,7 +5186,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>19</v>
@@ -4839,27 +5206,27 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>19</v>
@@ -4868,18 +5235,18 @@
         <v>23</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>19</v>
@@ -4890,7 +5257,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>28</v>
@@ -4910,13 +5277,13 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>14</v>
@@ -4930,7 +5297,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>28</v>
@@ -4941,7 +5308,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>30</v>
@@ -4961,13 +5328,13 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>14</v>
@@ -4981,7 +5348,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>30</v>
@@ -5001,7 +5368,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>30</v>
@@ -5021,7 +5388,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>30</v>
@@ -5079,21 +5446,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>37</v>
@@ -5104,7 +5471,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -5124,13 +5491,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
@@ -5144,7 +5511,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
@@ -5164,7 +5531,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -5175,7 +5542,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
@@ -5195,13 +5562,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>14</v>
@@ -5215,7 +5582,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>19</v>
@@ -5230,12 +5597,12 @@
         <v>40</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>19</v>
@@ -5255,7 +5622,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>19</v>
@@ -5266,7 +5633,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>28</v>
@@ -5286,13 +5653,13 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
@@ -5306,7 +5673,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>28</v>
@@ -5326,7 +5693,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>28</v>
@@ -5337,7 +5704,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>30</v>
@@ -5357,27 +5724,27 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
@@ -5389,15 +5756,15 @@
         <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>30</v>
@@ -5417,7 +5784,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>30</v>
@@ -5430,12 +5797,12 @@
         <v>40483.5</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>30</v>
@@ -5472,7 +5839,7 @@
         <v>0.0</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="AI22" s="3">
         <v>0.0</v>
@@ -5519,7 +5886,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>33</v>
@@ -5539,13 +5906,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>14</v>
@@ -5559,7 +5926,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>33</v>
@@ -5579,7 +5946,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>33</v>
@@ -5590,7 +5957,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>35</v>
@@ -5610,21 +5977,21 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>35</v>
@@ -5635,21 +6002,21 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>37</v>
@@ -5660,7 +6027,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -5680,13 +6047,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>14</v>
@@ -5700,7 +6067,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>12</v>
@@ -5720,7 +6087,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>12</v>
@@ -5731,7 +6098,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>19</v>
@@ -5751,27 +6118,27 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>19</v>
@@ -5791,7 +6158,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>19</v>
@@ -5811,7 +6178,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>19</v>
@@ -5824,12 +6191,12 @@
         <v>41160.0</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>19</v>
@@ -5866,7 +6233,7 @@
         <v>0.0</v>
       </c>
       <c r="AD41" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="AI41" s="3">
         <v>0.0</v>
@@ -5913,7 +6280,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>28</v>
@@ -5933,13 +6300,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>14</v>
@@ -5953,7 +6320,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>28</v>
@@ -5973,7 +6340,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>28</v>
@@ -5984,7 +6351,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>30</v>
@@ -6004,27 +6371,27 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>30</v>
@@ -6036,15 +6403,15 @@
         <v>14</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>30</v>
@@ -6064,7 +6431,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>30</v>
@@ -6077,12 +6444,12 @@
         <v>41286.0</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>30</v>
@@ -6119,7 +6486,7 @@
         <v>0.0</v>
       </c>
       <c r="AD51" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="AI51" s="3">
         <v>0.0</v>
@@ -6166,7 +6533,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>33</v>
@@ -6186,13 +6553,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>14</v>
@@ -6206,7 +6573,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>33</v>
@@ -6226,7 +6593,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>33</v>
@@ -6237,7 +6604,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>35</v>
@@ -6257,21 +6624,21 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>35</v>
@@ -6282,21 +6649,21 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>37</v>
@@ -6307,7 +6674,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>12</v>
@@ -6327,13 +6694,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>14</v>
@@ -6347,7 +6714,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>12</v>
@@ -6367,7 +6734,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>12</v>
@@ -6378,7 +6745,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>19</v>
@@ -6398,13 +6765,13 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>14</v>
@@ -6418,7 +6785,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>19</v>
@@ -6438,7 +6805,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>19</v>
@@ -6458,7 +6825,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>19</v>
@@ -6469,7 +6836,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>28</v>
@@ -6489,27 +6856,27 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>28</v>
@@ -6521,15 +6888,15 @@
         <v>14</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>28</v>
@@ -6542,12 +6909,12 @@
         <v>41264.0</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>28</v>
@@ -6584,7 +6951,7 @@
         <v>0.0</v>
       </c>
       <c r="AD74" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="AI74" s="3">
         <v>0.0</v>
@@ -6631,7 +6998,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>30</v>
@@ -6651,13 +7018,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>14</v>
@@ -6671,7 +7038,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>30</v>
@@ -6691,7 +7058,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>30</v>
@@ -6702,7 +7069,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>33</v>
@@ -6722,13 +7089,13 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>14</v>
@@ -6742,7 +7109,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>33</v>
@@ -6762,7 +7129,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>33</v>
@@ -6773,7 +7140,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>35</v>
@@ -6793,21 +7160,21 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>35</v>
@@ -6818,21 +7185,21 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>37</v>
@@ -6843,7 +7210,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>12</v>
@@ -6863,13 +7230,13 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>14</v>
@@ -6883,7 +7250,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>12</v>
@@ -6894,7 +7261,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>19</v>
@@ -6914,21 +7281,21 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>19</v>
@@ -6948,7 +7315,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>19</v>
@@ -6968,7 +7335,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>19</v>
@@ -6979,7 +7346,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>28</v>
@@ -6999,13 +7366,13 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>14</v>
@@ -7019,7 +7386,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>28</v>
@@ -7039,7 +7406,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>28</v>
@@ -7050,7 +7417,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>30</v>
@@ -7070,13 +7437,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>14</v>
@@ -7090,7 +7457,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>30</v>
@@ -7110,7 +7477,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>30</v>
@@ -7130,7 +7497,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>30</v>
@@ -7141,7 +7508,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>33</v>
@@ -7161,13 +7528,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>14</v>
@@ -7181,7 +7548,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>33</v>
@@ -7201,7 +7568,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>33</v>
@@ -7212,7 +7579,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>35</v>
@@ -7232,21 +7599,21 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>35</v>
@@ -7257,21 +7624,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>37</v>
@@ -7282,7 +7649,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>12</v>
@@ -7302,13 +7669,13 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>14</v>
@@ -7322,7 +7689,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>12</v>
@@ -7342,7 +7709,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>12</v>
@@ -7353,7 +7720,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>19</v>
@@ -7373,13 +7740,13 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>14</v>
@@ -7393,7 +7760,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>19</v>
@@ -7413,19 +7780,19 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>14</v>
@@ -7433,7 +7800,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>19</v>
@@ -7442,7 +7809,7 @@
         <v>23</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>25</v>
@@ -7453,7 +7820,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>19</v>
@@ -7511,21 +7878,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>37</v>
@@ -7536,7 +7903,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -7556,13 +7923,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
@@ -7576,7 +7943,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
@@ -7596,7 +7963,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -7607,7 +7974,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
@@ -7619,35 +7986,35 @@
         <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>19</v>
@@ -7659,15 +8026,15 @@
         <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>19</v>
@@ -7687,7 +8054,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>19</v>
@@ -7698,7 +8065,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>28</v>
@@ -7718,13 +8085,13 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
@@ -7738,7 +8105,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>28</v>
@@ -7749,7 +8116,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>30</v>
@@ -7769,13 +8136,13 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>14</v>
@@ -7789,7 +8156,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>30</v>
@@ -7809,7 +8176,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
@@ -7820,7 +8187,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>33</v>
@@ -7840,13 +8207,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>14</v>
@@ -7860,7 +8227,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>33</v>
@@ -7880,7 +8247,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>33</v>
@@ -7891,7 +8258,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>35</v>
@@ -7911,21 +8278,21 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>35</v>
@@ -7936,21 +8303,21 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>37</v>
@@ -7961,7 +8328,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>12</v>
@@ -7981,13 +8348,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>14</v>
@@ -8001,7 +8368,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>12</v>
@@ -8021,7 +8388,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -8032,7 +8399,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>19</v>
@@ -8044,35 +8411,35 @@
         <v>14</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>19</v>
@@ -8084,15 +8451,15 @@
         <v>14</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>19</v>
@@ -8112,7 +8479,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>19</v>
@@ -8123,7 +8490,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>28</v>
@@ -8143,13 +8510,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>14</v>
@@ -8163,7 +8530,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>28</v>
@@ -8183,7 +8550,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>28</v>
@@ -8194,7 +8561,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>30</v>
@@ -8206,35 +8573,35 @@
         <v>14</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>30</v>
@@ -8246,15 +8613,15 @@
         <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>30</v>
@@ -8274,7 +8641,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>30</v>
@@ -8285,7 +8652,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>33</v>
@@ -8297,35 +8664,35 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>33</v>
@@ -8336,7 +8703,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>35</v>
@@ -8356,21 +8723,21 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>35</v>
@@ -8381,21 +8748,21 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>37</v>
@@ -8406,7 +8773,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>12</v>
@@ -8426,13 +8793,13 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>14</v>
@@ -8446,7 +8813,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>12</v>
@@ -8466,7 +8833,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>12</v>
@@ -8477,7 +8844,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>19</v>
@@ -8497,13 +8864,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>14</v>
@@ -8517,7 +8884,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>19</v>
@@ -8537,7 +8904,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>19</v>
@@ -8546,18 +8913,18 @@
         <v>23</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>19</v>
@@ -8568,7 +8935,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>28</v>
@@ -8588,13 +8955,13 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>14</v>
@@ -8608,7 +8975,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>28</v>
@@ -8628,7 +8995,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>28</v>
@@ -8639,7 +9006,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>30</v>
@@ -8651,35 +9018,35 @@
         <v>14</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>30</v>
@@ -8691,15 +9058,15 @@
         <v>14</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>30</v>
@@ -8719,7 +9086,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>30</v>
@@ -8730,7 +9097,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>33</v>
@@ -8750,13 +9117,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>14</v>
@@ -8770,7 +9137,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>33</v>
@@ -8790,7 +9157,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>33</v>
@@ -8801,7 +9168,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>35</v>
@@ -8821,21 +9188,21 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>35</v>
@@ -8846,21 +9213,21 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>37</v>
@@ -8871,7 +9238,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>12</v>
@@ -8891,13 +9258,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>14</v>
@@ -8911,7 +9278,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>12</v>
@@ -8931,7 +9298,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>12</v>
@@ -8942,7 +9309,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>19</v>
@@ -8962,13 +9329,13 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>14</v>
@@ -8982,7 +9349,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>19</v>
@@ -9002,7 +9369,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>19</v>
@@ -9022,7 +9389,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>19</v>
@@ -9033,7 +9400,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>28</v>
@@ -9053,13 +9420,13 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>14</v>
@@ -9073,7 +9440,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>28</v>
@@ -9093,7 +9460,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>28</v>
@@ -9104,7 +9471,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>30</v>
@@ -9116,29 +9483,29 @@
         <v>14</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>30</v>
@@ -9150,15 +9517,15 @@
         <v>14</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>30</v>
@@ -9178,7 +9545,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>30</v>
@@ -9189,7 +9556,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>33</v>
@@ -9209,13 +9576,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>14</v>
@@ -9229,7 +9596,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>33</v>
@@ -9249,7 +9616,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>33</v>
@@ -9260,21 +9627,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>35</v>
@@ -9294,7 +9661,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>35</v>
@@ -9352,7 +9719,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>30</v>
@@ -9361,12 +9728,12 @@
         <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>30</v>
@@ -9377,27 +9744,27 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>181</v>
+        <v>45</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>33</v>
@@ -9409,35 +9776,35 @@
         <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>181</v>
+        <v>45</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>181</v>
+        <v>45</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>33</v>
@@ -9448,7 +9815,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>35</v>
@@ -9468,7 +9835,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>35</v>
@@ -9477,12 +9844,12 @@
         <v>17</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>35</v>
@@ -9493,7 +9860,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>37</v>
@@ -9502,12 +9869,12 @@
         <v>17</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>37</v>
@@ -9518,7 +9885,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
@@ -9538,7 +9905,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
@@ -9558,13 +9925,13 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>14</v>
@@ -9578,7 +9945,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>12</v>
@@ -9589,7 +9956,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>19</v>
@@ -9609,7 +9976,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>19</v>
@@ -9629,13 +9996,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>14</v>
@@ -9649,7 +10016,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>19</v>
@@ -9669,7 +10036,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>19</v>
@@ -9680,7 +10047,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>28</v>
@@ -9700,7 +10067,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>28</v>
@@ -9720,13 +10087,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>14</v>
@@ -9740,7 +10107,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>28</v>
@@ -9751,7 +10118,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>30</v>
@@ -9771,7 +10138,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>30</v>
@@ -9791,13 +10158,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>14</v>
@@ -9811,7 +10178,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>30</v>
@@ -9823,15 +10190,15 @@
         <v>24</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>30</v>
@@ -9842,7 +10209,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>33</v>
@@ -9862,13 +10229,13 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>14</v>
@@ -9882,7 +10249,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>33</v>
@@ -9902,7 +10269,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>33</v>
@@ -9913,7 +10280,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>35</v>
@@ -9933,21 +10300,21 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>35</v>
@@ -9958,21 +10325,21 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>37</v>
@@ -9983,7 +10350,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>12</v>
@@ -10003,13 +10370,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>14</v>
@@ -10023,7 +10390,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>12</v>
@@ -10034,7 +10401,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>19</v>
@@ -10046,35 +10413,35 @@
         <v>14</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>19</v>
@@ -10094,7 +10461,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>19</v>
@@ -10105,7 +10472,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>28</v>
@@ -10117,35 +10484,35 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>28</v>
@@ -10156,7 +10523,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>30</v>
@@ -10168,35 +10535,35 @@
         <v>14</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>30</v>
@@ -10211,12 +10578,12 @@
         <v>24</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>30</v>
@@ -10228,15 +10595,15 @@
         <v>24</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>30</v>
@@ -10247,7 +10614,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>33</v>
@@ -10267,13 +10634,13 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>14</v>
@@ -10287,7 +10654,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>33</v>
@@ -10307,7 +10674,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>33</v>
@@ -10318,7 +10685,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>35</v>
@@ -10338,21 +10705,21 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>35</v>
@@ -10363,21 +10730,21 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>37</v>
@@ -10388,7 +10755,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>12</v>
@@ -10408,13 +10775,13 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>14</v>
@@ -10428,7 +10795,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>12</v>
@@ -10439,7 +10806,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>19</v>
@@ -10459,13 +10826,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>14</v>
@@ -10479,7 +10846,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>19</v>
@@ -10499,7 +10866,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>19</v>
@@ -10519,7 +10886,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>19</v>
@@ -10530,7 +10897,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>28</v>
@@ -10542,35 +10909,35 @@
         <v>14</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>181</v>
+        <v>45</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>181</v>
+        <v>45</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>28</v>
@@ -10585,12 +10952,12 @@
         <v>21</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>28</v>
@@ -10601,7 +10968,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>30</v>
@@ -10621,13 +10988,13 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>14</v>
@@ -10641,7 +11008,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>30</v>
@@ -10661,7 +11028,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>30</v>
@@ -10672,7 +11039,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>33</v>
@@ -10684,35 +11051,35 @@
         <v>14</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>33</v>
@@ -10723,7 +11090,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>35</v>
@@ -10743,7 +11110,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>35</v>
@@ -10754,7 +11121,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>37</v>
@@ -10765,7 +11132,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>12</v>
@@ -10785,13 +11152,13 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>14</v>
@@ -10805,7 +11172,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>12</v>
@@ -10825,7 +11192,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>12</v>
@@ -10836,7 +11203,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>19</v>
@@ -10856,13 +11223,13 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>14</v>
@@ -10876,7 +11243,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>19</v>
@@ -10896,7 +11263,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>19</v>
@@ -10916,7 +11283,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>19</v>
@@ -10927,7 +11294,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>28</v>
@@ -10947,13 +11314,13 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>14</v>
@@ -10967,7 +11334,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>28</v>
@@ -10987,7 +11354,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>28</v>
@@ -10998,7 +11365,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>30</v>
@@ -11018,13 +11385,13 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>14</v>
@@ -11038,7 +11405,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>30</v>
@@ -11058,7 +11425,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>30</v>
@@ -11078,7 +11445,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>30</v>
@@ -11089,7 +11456,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>33</v>
@@ -11109,13 +11476,13 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>14</v>
@@ -11129,7 +11496,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>33</v>
@@ -11149,7 +11516,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>33</v>
@@ -11160,21 +11527,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>35</v>
@@ -11194,7 +11561,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>35</v>

--- a/google_data/Pobočky/Výroba/Databaze Výroba 2026.xlsx
+++ b/google_data/Pobočky/Výroba/Databaze Výroba 2026.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2827" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2867" uniqueCount="224">
   <si>
     <t>Datum</t>
   </si>
@@ -179,6 +179,12 @@
   </si>
   <si>
     <t>15.06.2026</t>
+  </si>
+  <si>
+    <t>16.06.2026</t>
+  </si>
+  <si>
+    <t>17.06.2026</t>
   </si>
   <si>
     <t>01.05.2026</t>
@@ -1901,6 +1907,148 @@
         <v>41614.75</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" s="3">
+        <v>41452.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H60" s="3">
+        <v>41614.75</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1950,7 +2098,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>33</v>
@@ -1970,13 +2118,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -1990,7 +2138,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>33</v>
@@ -2010,7 +2158,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>33</v>
@@ -2021,7 +2169,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>35</v>
@@ -2041,7 +2189,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>35</v>
@@ -2052,7 +2200,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>37</v>
@@ -2063,7 +2211,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -2083,13 +2231,13 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -2103,7 +2251,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>12</v>
@@ -2123,7 +2271,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>12</v>
@@ -2134,13 +2282,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>14</v>
@@ -2154,7 +2302,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>19</v>
@@ -2174,7 +2322,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>19</v>
@@ -2194,7 +2342,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>19</v>
@@ -2205,7 +2353,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>28</v>
@@ -2225,13 +2373,13 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>14</v>
@@ -2245,7 +2393,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>28</v>
@@ -2256,7 +2404,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>30</v>
@@ -2276,13 +2424,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>14</v>
@@ -2296,7 +2444,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>30</v>
@@ -2316,7 +2464,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>30</v>
@@ -2336,7 +2484,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>30</v>
@@ -2347,13 +2495,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>14</v>
@@ -2367,7 +2515,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>33</v>
@@ -2387,7 +2535,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>33</v>
@@ -2398,7 +2546,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>35</v>
@@ -2419,7 +2567,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>35</v>
@@ -2453,7 +2601,7 @@
         <v>0.0</v>
       </c>
       <c r="AD29" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AI29" s="3">
         <v>0.0</v>
@@ -2500,7 +2648,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>37</v>
@@ -2511,13 +2659,13 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>14</v>
@@ -2531,7 +2679,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -2551,7 +2699,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>12</v>
@@ -2562,13 +2710,13 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>14</v>
@@ -2577,12 +2725,12 @@
         <v>49</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>19</v>
@@ -2597,12 +2745,12 @@
         <v>49</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>19</v>
@@ -2622,7 +2770,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>19</v>
@@ -2633,13 +2781,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>14</v>
@@ -2653,7 +2801,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>28</v>
@@ -2673,7 +2821,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>28</v>
@@ -2684,13 +2832,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>14</v>
@@ -2704,7 +2852,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>30</v>
@@ -2724,7 +2872,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>30</v>
@@ -2744,7 +2892,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>30</v>
@@ -2755,13 +2903,13 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>14</v>
@@ -2775,7 +2923,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>33</v>
@@ -2795,7 +2943,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>33</v>
@@ -2806,7 +2954,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>35</v>
@@ -2817,7 +2965,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>37</v>
@@ -2828,7 +2976,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>12</v>
@@ -2848,13 +2996,13 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>14</v>
@@ -2868,7 +3016,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>12</v>
@@ -2879,7 +3027,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>19</v>
@@ -2899,13 +3047,13 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>14</v>
@@ -2919,7 +3067,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>19</v>
@@ -2939,7 +3087,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>19</v>
@@ -2959,7 +3107,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>19</v>
@@ -2970,13 +3118,13 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>14</v>
@@ -2990,7 +3138,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>28</v>
@@ -3010,7 +3158,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>28</v>
@@ -3030,7 +3178,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>28</v>
@@ -3041,13 +3189,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>14</v>
@@ -3061,7 +3209,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>30</v>
@@ -3081,7 +3229,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>30</v>
@@ -3101,7 +3249,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>30</v>
@@ -3121,7 +3269,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>30</v>
@@ -3132,7 +3280,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>33</v>
@@ -3152,13 +3300,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>14</v>
@@ -3172,7 +3320,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>33</v>
@@ -3192,7 +3340,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>33</v>
@@ -3203,7 +3351,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>35</v>
@@ -3223,7 +3371,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>35</v>
@@ -3234,7 +3382,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>37</v>
@@ -3245,7 +3393,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>12</v>
@@ -3265,7 +3413,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>12</v>
@@ -3285,7 +3433,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>12</v>
@@ -3296,7 +3444,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>19</v>
@@ -3316,7 +3464,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>19</v>
@@ -3336,7 +3484,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>19</v>
@@ -3356,7 +3504,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>19</v>
@@ -3367,7 +3515,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>28</v>
@@ -3387,7 +3535,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>28</v>
@@ -3407,7 +3555,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>28</v>
@@ -3418,7 +3566,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>30</v>
@@ -3438,7 +3586,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>30</v>
@@ -3458,7 +3606,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>30</v>
@@ -3478,7 +3626,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>30</v>
@@ -3489,7 +3637,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>33</v>
@@ -3509,7 +3657,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>33</v>
@@ -3529,7 +3677,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>33</v>
@@ -3540,7 +3688,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>35</v>
@@ -3560,7 +3708,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>35</v>
@@ -3571,7 +3719,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>37</v>
@@ -3629,7 +3777,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>28</v>
@@ -3649,13 +3797,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -3669,7 +3817,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>28</v>
@@ -3689,7 +3837,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>28</v>
@@ -3700,7 +3848,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>30</v>
@@ -3720,13 +3868,13 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>14</v>
@@ -3740,7 +3888,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>30</v>
@@ -3760,7 +3908,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>30</v>
@@ -3780,7 +3928,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>30</v>
@@ -3791,7 +3939,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>33</v>
@@ -3811,13 +3959,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -3831,7 +3979,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>33</v>
@@ -3851,7 +3999,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>33</v>
@@ -3862,7 +4010,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>35</v>
@@ -3882,7 +4030,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>35</v>
@@ -3893,7 +4041,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>37</v>
@@ -3904,7 +4052,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>12</v>
@@ -3924,13 +4072,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>14</v>
@@ -3944,7 +4092,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>12</v>
@@ -3964,7 +4112,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>12</v>
@@ -3975,7 +4123,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>19</v>
@@ -3995,13 +4143,13 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>14</v>
@@ -4015,7 +4163,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>19</v>
@@ -4035,13 +4183,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>24</v>
@@ -4050,12 +4198,12 @@
         <v>15</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>19</v>
@@ -4070,12 +4218,12 @@
         <v>25</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>19</v>
@@ -4086,7 +4234,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>28</v>
@@ -4106,13 +4254,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>14</v>
@@ -4126,7 +4274,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>28</v>
@@ -4146,7 +4294,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>28</v>
@@ -4157,7 +4305,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>30</v>
@@ -4177,13 +4325,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>14</v>
@@ -4197,7 +4345,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>30</v>
@@ -4217,7 +4365,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>30</v>
@@ -4237,7 +4385,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>30</v>
@@ -4248,7 +4396,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>33</v>
@@ -4263,18 +4411,18 @@
         <v>49</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>14</v>
@@ -4283,12 +4431,12 @@
         <v>49</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>33</v>
@@ -4303,12 +4451,12 @@
         <v>49</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>33</v>
@@ -4319,7 +4467,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>35</v>
@@ -4339,7 +4487,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>35</v>
@@ -4350,7 +4498,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>37</v>
@@ -4361,7 +4509,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>12</v>
@@ -4381,7 +4529,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>12</v>
@@ -4401,7 +4549,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>12</v>
@@ -4412,7 +4560,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>19</v>
@@ -4432,7 +4580,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>19</v>
@@ -4452,19 +4600,19 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>14</v>
@@ -4472,7 +4620,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>19</v>
@@ -4481,10 +4629,10 @@
         <v>23</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>14</v>
@@ -4492,7 +4640,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>19</v>
@@ -4503,13 +4651,13 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>14</v>
@@ -4523,7 +4671,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>28</v>
@@ -4543,7 +4691,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>28</v>
@@ -4563,7 +4711,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>28</v>
@@ -4574,7 +4722,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>30</v>
@@ -4594,13 +4742,13 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>14</v>
@@ -4614,7 +4762,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>30</v>
@@ -4634,7 +4782,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>30</v>
@@ -4654,7 +4802,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>30</v>
@@ -4665,7 +4813,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>33</v>
@@ -4685,13 +4833,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>14</v>
@@ -4705,7 +4853,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>33</v>
@@ -4716,7 +4864,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>35</v>
@@ -4736,7 +4884,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>35</v>
@@ -4747,7 +4895,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>37</v>
@@ -4758,7 +4906,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>12</v>
@@ -4778,13 +4926,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>14</v>
@@ -4798,7 +4946,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>12</v>
@@ -4809,7 +4957,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>19</v>
@@ -4829,13 +4977,13 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>14</v>
@@ -4849,19 +4997,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>14</v>
@@ -4869,7 +5017,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>19</v>
@@ -4878,18 +5026,18 @@
         <v>23</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>19</v>
@@ -4900,7 +5048,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>28</v>
@@ -4920,13 +5068,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>14</v>
@@ -4940,7 +5088,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>28</v>
@@ -4951,7 +5099,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>30</v>
@@ -4971,13 +5119,13 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>14</v>
@@ -4991,7 +5139,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>30</v>
@@ -5011,7 +5159,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>30</v>
@@ -5022,7 +5170,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>33</v>
@@ -5042,13 +5190,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>14</v>
@@ -5062,7 +5210,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>33</v>
@@ -5073,7 +5221,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>35</v>
@@ -5093,7 +5241,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>35</v>
@@ -5104,7 +5252,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>37</v>
@@ -5115,7 +5263,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>12</v>
@@ -5135,13 +5283,13 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>14</v>
@@ -5155,7 +5303,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>12</v>
@@ -5166,7 +5314,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>19</v>
@@ -5186,7 +5334,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>19</v>
@@ -5206,27 +5354,27 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>19</v>
@@ -5235,18 +5383,18 @@
         <v>23</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>19</v>
@@ -5257,7 +5405,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>28</v>
@@ -5277,13 +5425,13 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>14</v>
@@ -5297,7 +5445,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>28</v>
@@ -5308,7 +5456,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>30</v>
@@ -5328,13 +5476,13 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>14</v>
@@ -5348,7 +5496,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>30</v>
@@ -5368,7 +5516,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>30</v>
@@ -5388,7 +5536,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>30</v>
@@ -5446,21 +5594,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>37</v>
@@ -5471,7 +5619,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -5491,13 +5639,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
@@ -5511,7 +5659,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
@@ -5531,7 +5679,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -5542,7 +5690,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
@@ -5562,13 +5710,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>14</v>
@@ -5582,7 +5730,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>19</v>
@@ -5597,12 +5745,12 @@
         <v>40</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>19</v>
@@ -5622,7 +5770,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>19</v>
@@ -5633,7 +5781,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>28</v>
@@ -5653,13 +5801,13 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
@@ -5673,7 +5821,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>28</v>
@@ -5693,7 +5841,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>28</v>
@@ -5704,7 +5852,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>30</v>
@@ -5724,27 +5872,27 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
@@ -5756,15 +5904,15 @@
         <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>30</v>
@@ -5784,7 +5932,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>30</v>
@@ -5797,12 +5945,12 @@
         <v>40483.5</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>30</v>
@@ -5839,7 +5987,7 @@
         <v>0.0</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AI22" s="3">
         <v>0.0</v>
@@ -5886,7 +6034,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>33</v>
@@ -5906,13 +6054,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>14</v>
@@ -5926,7 +6074,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>33</v>
@@ -5946,7 +6094,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>33</v>
@@ -5957,7 +6105,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>35</v>
@@ -5977,21 +6125,21 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>35</v>
@@ -6002,21 +6150,21 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>37</v>
@@ -6027,7 +6175,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -6047,13 +6195,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>14</v>
@@ -6067,7 +6215,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>12</v>
@@ -6087,7 +6235,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>12</v>
@@ -6098,7 +6246,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>19</v>
@@ -6118,13 +6266,13 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>14</v>
@@ -6133,12 +6281,12 @@
         <v>49</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>19</v>
@@ -6158,7 +6306,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>19</v>
@@ -6178,7 +6326,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>19</v>
@@ -6191,12 +6339,12 @@
         <v>41160.0</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>19</v>
@@ -6233,7 +6381,7 @@
         <v>0.0</v>
       </c>
       <c r="AD41" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AI41" s="3">
         <v>0.0</v>
@@ -6280,7 +6428,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>28</v>
@@ -6300,13 +6448,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>14</v>
@@ -6320,7 +6468,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>28</v>
@@ -6340,7 +6488,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>28</v>
@@ -6351,7 +6499,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>30</v>
@@ -6371,13 +6519,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>14</v>
@@ -6386,12 +6534,12 @@
         <v>49</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>30</v>
@@ -6406,12 +6554,12 @@
         <v>49</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>30</v>
@@ -6431,7 +6579,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>30</v>
@@ -6444,12 +6592,12 @@
         <v>41286.0</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>30</v>
@@ -6486,7 +6634,7 @@
         <v>0.0</v>
       </c>
       <c r="AD51" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AI51" s="3">
         <v>0.0</v>
@@ -6533,7 +6681,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>33</v>
@@ -6553,13 +6701,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>14</v>
@@ -6573,7 +6721,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>33</v>
@@ -6593,7 +6741,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>33</v>
@@ -6604,7 +6752,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>35</v>
@@ -6624,21 +6772,21 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>35</v>
@@ -6649,21 +6797,21 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>37</v>
@@ -6674,7 +6822,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>12</v>
@@ -6694,13 +6842,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>14</v>
@@ -6714,7 +6862,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>12</v>
@@ -6734,7 +6882,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>12</v>
@@ -6745,7 +6893,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>19</v>
@@ -6765,13 +6913,13 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>14</v>
@@ -6785,7 +6933,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>19</v>
@@ -6805,7 +6953,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>19</v>
@@ -6825,7 +6973,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>19</v>
@@ -6836,7 +6984,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>28</v>
@@ -6856,13 +7004,13 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>14</v>
@@ -6871,12 +7019,12 @@
         <v>49</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>28</v>
@@ -6891,12 +7039,12 @@
         <v>49</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>28</v>
@@ -6909,12 +7057,12 @@
         <v>41264.0</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>28</v>
@@ -6951,7 +7099,7 @@
         <v>0.0</v>
       </c>
       <c r="AD74" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AI74" s="3">
         <v>0.0</v>
@@ -6998,7 +7146,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>30</v>
@@ -7018,13 +7166,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>14</v>
@@ -7038,7 +7186,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>30</v>
@@ -7058,7 +7206,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>30</v>
@@ -7069,7 +7217,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>33</v>
@@ -7089,13 +7237,13 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>14</v>
@@ -7109,7 +7257,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>33</v>
@@ -7129,7 +7277,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>33</v>
@@ -7140,7 +7288,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>35</v>
@@ -7160,21 +7308,21 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>35</v>
@@ -7185,21 +7333,21 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>37</v>
@@ -7210,7 +7358,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>12</v>
@@ -7230,13 +7378,13 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>14</v>
@@ -7250,7 +7398,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>12</v>
@@ -7261,7 +7409,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>19</v>
@@ -7281,21 +7429,21 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>19</v>
@@ -7315,7 +7463,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>19</v>
@@ -7335,7 +7483,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>19</v>
@@ -7346,7 +7494,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>28</v>
@@ -7366,13 +7514,13 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>14</v>
@@ -7386,7 +7534,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>28</v>
@@ -7406,7 +7554,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>28</v>
@@ -7417,7 +7565,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>30</v>
@@ -7437,13 +7585,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>14</v>
@@ -7457,7 +7605,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>30</v>
@@ -7477,7 +7625,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>30</v>
@@ -7497,7 +7645,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>30</v>
@@ -7508,7 +7656,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>33</v>
@@ -7528,13 +7676,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>14</v>
@@ -7548,7 +7696,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>33</v>
@@ -7568,7 +7716,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>33</v>
@@ -7579,7 +7727,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>35</v>
@@ -7599,21 +7747,21 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>35</v>
@@ -7624,21 +7772,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>37</v>
@@ -7649,7 +7797,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>12</v>
@@ -7669,13 +7817,13 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>14</v>
@@ -7689,7 +7837,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>12</v>
@@ -7709,7 +7857,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>12</v>
@@ -7720,7 +7868,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>19</v>
@@ -7740,13 +7888,13 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>14</v>
@@ -7760,7 +7908,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>19</v>
@@ -7780,19 +7928,19 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>14</v>
@@ -7800,7 +7948,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>19</v>
@@ -7809,7 +7957,7 @@
         <v>23</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>25</v>
@@ -7820,7 +7968,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>19</v>
@@ -7878,21 +8026,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>37</v>
@@ -7903,7 +8051,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -7923,13 +8071,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
@@ -7943,7 +8091,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
@@ -7963,7 +8111,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -7974,7 +8122,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
@@ -7986,35 +8134,35 @@
         <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>19</v>
@@ -8026,15 +8174,15 @@
         <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>19</v>
@@ -8054,7 +8202,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>19</v>
@@ -8065,7 +8213,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>28</v>
@@ -8085,13 +8233,13 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
@@ -8105,7 +8253,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>28</v>
@@ -8116,7 +8264,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>30</v>
@@ -8136,13 +8284,13 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>14</v>
@@ -8156,7 +8304,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>30</v>
@@ -8176,7 +8324,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
@@ -8187,7 +8335,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>33</v>
@@ -8207,13 +8355,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>14</v>
@@ -8227,7 +8375,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>33</v>
@@ -8247,7 +8395,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>33</v>
@@ -8258,7 +8406,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>35</v>
@@ -8278,21 +8426,21 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>35</v>
@@ -8303,21 +8451,21 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>37</v>
@@ -8328,7 +8476,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>12</v>
@@ -8348,13 +8496,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>14</v>
@@ -8368,7 +8516,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>12</v>
@@ -8388,7 +8536,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -8399,7 +8547,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>19</v>
@@ -8414,18 +8562,18 @@
         <v>49</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>14</v>
@@ -8434,12 +8582,12 @@
         <v>49</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>19</v>
@@ -8454,12 +8602,12 @@
         <v>49</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>19</v>
@@ -8479,7 +8627,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>19</v>
@@ -8490,7 +8638,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>28</v>
@@ -8510,13 +8658,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>14</v>
@@ -8530,7 +8678,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>28</v>
@@ -8550,7 +8698,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>28</v>
@@ -8561,7 +8709,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>30</v>
@@ -8573,35 +8721,35 @@
         <v>14</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>30</v>
@@ -8613,15 +8761,15 @@
         <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>30</v>
@@ -8641,7 +8789,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>30</v>
@@ -8652,7 +8800,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>33</v>
@@ -8667,18 +8815,18 @@
         <v>49</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>14</v>
@@ -8687,12 +8835,12 @@
         <v>49</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>33</v>
@@ -8703,7 +8851,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>35</v>
@@ -8723,21 +8871,21 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>35</v>
@@ -8748,21 +8896,21 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>37</v>
@@ -8773,7 +8921,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>12</v>
@@ -8793,13 +8941,13 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>14</v>
@@ -8813,7 +8961,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>12</v>
@@ -8833,7 +8981,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>12</v>
@@ -8844,7 +8992,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>19</v>
@@ -8864,13 +9012,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>14</v>
@@ -8884,7 +9032,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>19</v>
@@ -8904,7 +9052,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>19</v>
@@ -8924,7 +9072,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>19</v>
@@ -8935,7 +9083,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>28</v>
@@ -8955,13 +9103,13 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>14</v>
@@ -8975,7 +9123,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>28</v>
@@ -8995,7 +9143,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>28</v>
@@ -9006,7 +9154,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>30</v>
@@ -9021,18 +9169,18 @@
         <v>49</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>14</v>
@@ -9041,12 +9189,12 @@
         <v>49</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>30</v>
@@ -9061,12 +9209,12 @@
         <v>49</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>30</v>
@@ -9086,7 +9234,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>30</v>
@@ -9097,7 +9245,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>33</v>
@@ -9117,13 +9265,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>14</v>
@@ -9137,7 +9285,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>33</v>
@@ -9157,7 +9305,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>33</v>
@@ -9168,7 +9316,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>35</v>
@@ -9188,21 +9336,21 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>35</v>
@@ -9213,21 +9361,21 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>37</v>
@@ -9238,7 +9386,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>12</v>
@@ -9258,13 +9406,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>14</v>
@@ -9278,7 +9426,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>12</v>
@@ -9298,7 +9446,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>12</v>
@@ -9309,7 +9457,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>19</v>
@@ -9329,13 +9477,13 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>14</v>
@@ -9349,7 +9497,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>19</v>
@@ -9369,7 +9517,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>19</v>
@@ -9389,7 +9537,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>19</v>
@@ -9400,7 +9548,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>28</v>
@@ -9420,13 +9568,13 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>14</v>
@@ -9440,7 +9588,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>28</v>
@@ -9460,7 +9608,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>28</v>
@@ -9471,7 +9619,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>30</v>
@@ -9486,26 +9634,26 @@
         <v>49</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>30</v>
@@ -9520,12 +9668,12 @@
         <v>49</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>30</v>
@@ -9545,7 +9693,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>30</v>
@@ -9556,7 +9704,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>33</v>
@@ -9576,13 +9724,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>14</v>
@@ -9596,7 +9744,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>33</v>
@@ -9616,7 +9764,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>33</v>
@@ -9627,21 +9775,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>35</v>
@@ -9661,7 +9809,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>35</v>
@@ -9719,7 +9867,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>30</v>
@@ -9728,12 +9876,12 @@
         <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>30</v>
@@ -9744,13 +9892,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
@@ -9764,7 +9912,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>33</v>
@@ -9784,13 +9932,13 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>14</v>
@@ -9804,7 +9952,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>33</v>
@@ -9815,7 +9963,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>35</v>
@@ -9835,7 +9983,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>35</v>
@@ -9844,12 +9992,12 @@
         <v>17</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>35</v>
@@ -9860,7 +10008,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>37</v>
@@ -9869,12 +10017,12 @@
         <v>17</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>37</v>
@@ -9885,7 +10033,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
@@ -9905,7 +10053,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
@@ -9925,13 +10073,13 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>14</v>
@@ -9945,7 +10093,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>12</v>
@@ -9956,7 +10104,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>19</v>
@@ -9976,7 +10124,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>19</v>
@@ -9996,13 +10144,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>14</v>
@@ -10016,7 +10164,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>19</v>
@@ -10036,7 +10184,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>19</v>
@@ -10047,7 +10195,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>28</v>
@@ -10067,7 +10215,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>28</v>
@@ -10087,13 +10235,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>14</v>
@@ -10107,7 +10255,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>28</v>
@@ -10118,7 +10266,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>30</v>
@@ -10138,7 +10286,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>30</v>
@@ -10158,13 +10306,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>14</v>
@@ -10178,7 +10326,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>30</v>
@@ -10190,15 +10338,15 @@
         <v>24</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>30</v>
@@ -10209,7 +10357,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>33</v>
@@ -10229,13 +10377,13 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>14</v>
@@ -10249,7 +10397,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>33</v>
@@ -10269,7 +10417,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>33</v>
@@ -10280,7 +10428,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>35</v>
@@ -10300,21 +10448,21 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>35</v>
@@ -10325,21 +10473,21 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>37</v>
@@ -10350,7 +10498,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>12</v>
@@ -10370,13 +10518,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>14</v>
@@ -10390,7 +10538,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>12</v>
@@ -10401,7 +10549,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>19</v>
@@ -10416,18 +10564,18 @@
         <v>49</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>14</v>
@@ -10436,12 +10584,12 @@
         <v>49</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>19</v>
@@ -10461,7 +10609,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>19</v>
@@ -10472,7 +10620,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>28</v>
@@ -10487,18 +10635,18 @@
         <v>49</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>14</v>
@@ -10507,12 +10655,12 @@
         <v>49</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>28</v>
@@ -10523,7 +10671,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>30</v>
@@ -10538,18 +10686,18 @@
         <v>49</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>14</v>
@@ -10558,12 +10706,12 @@
         <v>49</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>30</v>
@@ -10578,12 +10726,12 @@
         <v>24</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>30</v>
@@ -10595,15 +10743,15 @@
         <v>24</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>30</v>
@@ -10614,7 +10762,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>33</v>
@@ -10634,13 +10782,13 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>14</v>
@@ -10654,7 +10802,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>33</v>
@@ -10674,7 +10822,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>33</v>
@@ -10685,7 +10833,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>35</v>
@@ -10705,21 +10853,21 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>35</v>
@@ -10730,21 +10878,21 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>37</v>
@@ -10755,7 +10903,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>12</v>
@@ -10775,13 +10923,13 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>14</v>
@@ -10795,7 +10943,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>12</v>
@@ -10806,7 +10954,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>19</v>
@@ -10826,13 +10974,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>14</v>
@@ -10846,7 +10994,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>19</v>
@@ -10866,7 +11014,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>19</v>
@@ -10886,7 +11034,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>19</v>
@@ -10897,7 +11045,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>28</v>
@@ -10917,13 +11065,13 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>14</v>
@@ -10937,7 +11085,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>28</v>
@@ -10952,12 +11100,12 @@
         <v>21</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>28</v>
@@ -10968,7 +11116,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>30</v>
@@ -10988,13 +11136,13 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>14</v>
@@ -11008,7 +11156,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>30</v>
@@ -11028,7 +11176,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>30</v>
@@ -11039,7 +11187,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>33</v>
@@ -11054,18 +11202,18 @@
         <v>49</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>14</v>
@@ -11074,12 +11222,12 @@
         <v>49</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>33</v>
@@ -11090,7 +11238,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>35</v>
@@ -11110,7 +11258,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>35</v>
@@ -11121,7 +11269,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>37</v>
@@ -11132,7 +11280,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>12</v>
@@ -11152,13 +11300,13 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>14</v>
@@ -11172,7 +11320,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>12</v>
@@ -11192,7 +11340,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>12</v>
@@ -11203,7 +11351,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>19</v>
@@ -11223,13 +11371,13 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>14</v>
@@ -11243,7 +11391,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>19</v>
@@ -11263,7 +11411,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>19</v>
@@ -11283,7 +11431,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>19</v>
@@ -11294,7 +11442,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>28</v>
@@ -11314,13 +11462,13 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>14</v>
@@ -11334,7 +11482,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>28</v>
@@ -11354,7 +11502,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>28</v>
@@ -11365,7 +11513,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>30</v>
@@ -11385,13 +11533,13 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>14</v>
@@ -11405,7 +11553,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>30</v>
@@ -11425,7 +11573,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>30</v>
@@ -11445,7 +11593,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>30</v>
@@ -11456,7 +11604,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>33</v>
@@ -11476,13 +11624,13 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>14</v>
@@ -11496,7 +11644,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>33</v>
@@ -11516,7 +11664,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>33</v>
@@ -11527,21 +11675,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>35</v>
@@ -11561,7 +11709,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>35</v>

--- a/google_data/Pobočky/Výroba/Databaze Výroba 2026.xlsx
+++ b/google_data/Pobočky/Výroba/Databaze Výroba 2026.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2867" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2921" uniqueCount="227">
   <si>
     <t>Datum</t>
   </si>
@@ -187,6 +187,24 @@
     <t>17.06.2026</t>
   </si>
   <si>
+    <t>18.06.2026</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>19.06.2026</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>20.06.2026</t>
+  </si>
+  <si>
     <t>01.05.2026</t>
   </si>
   <si>
@@ -391,9 +409,6 @@
     <t>28.04.2026</t>
   </si>
   <si>
-    <t>16:00</t>
-  </si>
-  <si>
     <t>29.04.2026</t>
   </si>
   <si>
@@ -419,12 +434,6 @@
   </si>
   <si>
     <t>05.03.2026</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>06:30</t>
   </si>
   <si>
     <t>06.03.2026</t>
@@ -2049,6 +2058,199 @@
         <v>41614.75</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H65" s="3">
+        <v>41755.75</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H69" s="3">
+        <v>41899.0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H71" s="3">
+        <v>40784.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2098,7 +2300,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>33</v>
@@ -2118,13 +2320,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -2138,7 +2340,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>33</v>
@@ -2158,7 +2360,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>33</v>
@@ -2169,7 +2371,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>35</v>
@@ -2189,7 +2391,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>35</v>
@@ -2200,7 +2402,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>37</v>
@@ -2211,7 +2413,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -2231,13 +2433,13 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -2251,7 +2453,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>12</v>
@@ -2271,7 +2473,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>12</v>
@@ -2282,13 +2484,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>14</v>
@@ -2302,7 +2504,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>19</v>
@@ -2322,7 +2524,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>19</v>
@@ -2342,7 +2544,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>19</v>
@@ -2353,7 +2555,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>28</v>
@@ -2373,13 +2575,13 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>14</v>
@@ -2393,7 +2595,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>28</v>
@@ -2404,7 +2606,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>30</v>
@@ -2424,13 +2626,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>14</v>
@@ -2444,7 +2646,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>30</v>
@@ -2464,7 +2666,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>30</v>
@@ -2484,7 +2686,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>30</v>
@@ -2495,13 +2697,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>14</v>
@@ -2515,7 +2717,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>33</v>
@@ -2535,7 +2737,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>33</v>
@@ -2546,7 +2748,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>35</v>
@@ -2567,7 +2769,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>35</v>
@@ -2601,7 +2803,7 @@
         <v>0.0</v>
       </c>
       <c r="AD29" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="AI29" s="3">
         <v>0.0</v>
@@ -2648,7 +2850,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>37</v>
@@ -2659,13 +2861,13 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>14</v>
@@ -2679,7 +2881,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -2699,7 +2901,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>12</v>
@@ -2710,13 +2912,13 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>14</v>
@@ -2725,12 +2927,12 @@
         <v>49</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>19</v>
@@ -2745,12 +2947,12 @@
         <v>49</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>19</v>
@@ -2770,7 +2972,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>19</v>
@@ -2781,13 +2983,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>14</v>
@@ -2801,7 +3003,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>28</v>
@@ -2821,7 +3023,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>28</v>
@@ -2832,13 +3034,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>14</v>
@@ -2852,7 +3054,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>30</v>
@@ -2872,7 +3074,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>30</v>
@@ -2892,7 +3094,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>30</v>
@@ -2903,13 +3105,13 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>14</v>
@@ -2923,7 +3125,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>33</v>
@@ -2943,7 +3145,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>33</v>
@@ -2954,7 +3156,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>35</v>
@@ -2965,7 +3167,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>37</v>
@@ -2976,7 +3178,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>12</v>
@@ -2996,13 +3198,13 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>14</v>
@@ -3016,7 +3218,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>12</v>
@@ -3027,7 +3229,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>19</v>
@@ -3047,13 +3249,13 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>14</v>
@@ -3067,7 +3269,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>19</v>
@@ -3087,7 +3289,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>19</v>
@@ -3107,7 +3309,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>19</v>
@@ -3118,13 +3320,13 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>14</v>
@@ -3138,7 +3340,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>28</v>
@@ -3158,7 +3360,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>28</v>
@@ -3178,7 +3380,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>28</v>
@@ -3189,13 +3391,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>14</v>
@@ -3209,7 +3411,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>30</v>
@@ -3229,7 +3431,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>30</v>
@@ -3249,7 +3451,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>30</v>
@@ -3269,7 +3471,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>30</v>
@@ -3280,7 +3482,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>33</v>
@@ -3300,13 +3502,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>14</v>
@@ -3320,7 +3522,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>33</v>
@@ -3340,7 +3542,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>33</v>
@@ -3351,7 +3553,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>35</v>
@@ -3371,7 +3573,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>35</v>
@@ -3382,7 +3584,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>37</v>
@@ -3393,7 +3595,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>12</v>
@@ -3413,7 +3615,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>12</v>
@@ -3433,7 +3635,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>12</v>
@@ -3444,7 +3646,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>19</v>
@@ -3464,7 +3666,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>19</v>
@@ -3484,7 +3686,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>19</v>
@@ -3504,7 +3706,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>19</v>
@@ -3515,7 +3717,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>28</v>
@@ -3535,7 +3737,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>28</v>
@@ -3555,7 +3757,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>28</v>
@@ -3566,7 +3768,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>30</v>
@@ -3586,7 +3788,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>30</v>
@@ -3606,7 +3808,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>30</v>
@@ -3626,7 +3828,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>30</v>
@@ -3637,7 +3839,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>33</v>
@@ -3657,7 +3859,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>33</v>
@@ -3677,7 +3879,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>33</v>
@@ -3688,7 +3890,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>35</v>
@@ -3708,7 +3910,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>35</v>
@@ -3719,7 +3921,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>37</v>
@@ -3777,7 +3979,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>28</v>
@@ -3797,13 +3999,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -3817,7 +4019,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>28</v>
@@ -3837,7 +4039,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>28</v>
@@ -3848,7 +4050,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>30</v>
@@ -3868,13 +4070,13 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>14</v>
@@ -3888,7 +4090,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>30</v>
@@ -3908,7 +4110,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>30</v>
@@ -3928,7 +4130,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>30</v>
@@ -3939,7 +4141,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>33</v>
@@ -3959,13 +4161,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -3979,7 +4181,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>33</v>
@@ -3999,7 +4201,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>33</v>
@@ -4010,7 +4212,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>35</v>
@@ -4030,7 +4232,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>35</v>
@@ -4041,7 +4243,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>37</v>
@@ -4052,7 +4254,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>12</v>
@@ -4072,13 +4274,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>14</v>
@@ -4092,7 +4294,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>12</v>
@@ -4112,7 +4314,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>12</v>
@@ -4123,7 +4325,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>19</v>
@@ -4143,13 +4345,13 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>14</v>
@@ -4163,7 +4365,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>19</v>
@@ -4183,13 +4385,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>24</v>
@@ -4198,12 +4400,12 @@
         <v>15</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>19</v>
@@ -4218,12 +4420,12 @@
         <v>25</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>19</v>
@@ -4234,7 +4436,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>28</v>
@@ -4254,13 +4456,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>14</v>
@@ -4274,7 +4476,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>28</v>
@@ -4294,7 +4496,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>28</v>
@@ -4305,7 +4507,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>30</v>
@@ -4325,13 +4527,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>14</v>
@@ -4345,7 +4547,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>30</v>
@@ -4365,7 +4567,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>30</v>
@@ -4385,7 +4587,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>30</v>
@@ -4396,7 +4598,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>33</v>
@@ -4411,18 +4613,18 @@
         <v>49</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>14</v>
@@ -4431,12 +4633,12 @@
         <v>49</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>33</v>
@@ -4451,12 +4653,12 @@
         <v>49</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>33</v>
@@ -4467,7 +4669,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>35</v>
@@ -4487,7 +4689,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>35</v>
@@ -4498,7 +4700,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>37</v>
@@ -4509,7 +4711,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>12</v>
@@ -4529,7 +4731,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>12</v>
@@ -4549,7 +4751,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>12</v>
@@ -4560,7 +4762,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>19</v>
@@ -4580,7 +4782,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>19</v>
@@ -4600,19 +4802,19 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>14</v>
@@ -4620,7 +4822,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>19</v>
@@ -4629,10 +4831,10 @@
         <v>23</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>14</v>
@@ -4640,7 +4842,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>19</v>
@@ -4651,13 +4853,13 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>14</v>
@@ -4671,7 +4873,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>28</v>
@@ -4691,7 +4893,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>28</v>
@@ -4711,7 +4913,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>28</v>
@@ -4722,7 +4924,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>30</v>
@@ -4742,13 +4944,13 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>14</v>
@@ -4762,7 +4964,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>30</v>
@@ -4782,7 +4984,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>30</v>
@@ -4802,7 +5004,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>30</v>
@@ -4813,7 +5015,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>33</v>
@@ -4833,13 +5035,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>14</v>
@@ -4853,7 +5055,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>33</v>
@@ -4864,7 +5066,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>35</v>
@@ -4884,7 +5086,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>35</v>
@@ -4895,7 +5097,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>37</v>
@@ -4906,7 +5108,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>12</v>
@@ -4926,13 +5128,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>14</v>
@@ -4946,7 +5148,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>12</v>
@@ -4957,7 +5159,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>19</v>
@@ -4977,13 +5179,13 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>14</v>
@@ -4997,19 +5199,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>14</v>
@@ -5017,7 +5219,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>19</v>
@@ -5026,18 +5228,18 @@
         <v>23</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>19</v>
@@ -5048,7 +5250,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>28</v>
@@ -5068,13 +5270,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>14</v>
@@ -5088,7 +5290,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>28</v>
@@ -5099,7 +5301,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>30</v>
@@ -5119,13 +5321,13 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>14</v>
@@ -5139,7 +5341,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>30</v>
@@ -5159,7 +5361,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>30</v>
@@ -5170,7 +5372,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>33</v>
@@ -5190,13 +5392,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>14</v>
@@ -5210,7 +5412,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>33</v>
@@ -5221,7 +5423,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>35</v>
@@ -5241,7 +5443,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>35</v>
@@ -5252,7 +5454,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>37</v>
@@ -5263,7 +5465,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>12</v>
@@ -5283,13 +5485,13 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>14</v>
@@ -5303,7 +5505,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>12</v>
@@ -5314,7 +5516,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>19</v>
@@ -5334,7 +5536,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>19</v>
@@ -5354,27 +5556,27 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>19</v>
@@ -5383,18 +5585,18 @@
         <v>23</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>19</v>
@@ -5405,7 +5607,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>28</v>
@@ -5425,13 +5627,13 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>14</v>
@@ -5445,7 +5647,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>28</v>
@@ -5456,7 +5658,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>30</v>
@@ -5476,13 +5678,13 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>14</v>
@@ -5496,7 +5698,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>30</v>
@@ -5516,7 +5718,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>30</v>
@@ -5536,7 +5738,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>30</v>
@@ -5594,21 +5796,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>37</v>
@@ -5619,7 +5821,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -5639,13 +5841,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
@@ -5659,7 +5861,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
@@ -5679,7 +5881,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -5690,7 +5892,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
@@ -5710,13 +5912,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>14</v>
@@ -5730,7 +5932,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>19</v>
@@ -5745,12 +5947,12 @@
         <v>40</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>19</v>
@@ -5770,7 +5972,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>19</v>
@@ -5781,7 +5983,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>28</v>
@@ -5801,13 +6003,13 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
@@ -5821,7 +6023,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>28</v>
@@ -5841,7 +6043,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>28</v>
@@ -5852,7 +6054,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>30</v>
@@ -5872,27 +6074,27 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="G18" s="2" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
@@ -5904,15 +6106,15 @@
         <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>30</v>
@@ -5932,7 +6134,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>30</v>
@@ -5945,12 +6147,12 @@
         <v>40483.5</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>30</v>
@@ -5987,7 +6189,7 @@
         <v>0.0</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="AI22" s="3">
         <v>0.0</v>
@@ -6034,7 +6236,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>33</v>
@@ -6054,13 +6256,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>14</v>
@@ -6074,7 +6276,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>33</v>
@@ -6094,7 +6296,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>33</v>
@@ -6105,7 +6307,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>35</v>
@@ -6125,21 +6327,21 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>35</v>
@@ -6150,21 +6352,21 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>37</v>
@@ -6175,7 +6377,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -6195,13 +6397,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>14</v>
@@ -6215,7 +6417,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>12</v>
@@ -6235,7 +6437,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>12</v>
@@ -6246,7 +6448,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>19</v>
@@ -6266,13 +6468,13 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>14</v>
@@ -6281,12 +6483,12 @@
         <v>49</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>19</v>
@@ -6306,7 +6508,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>19</v>
@@ -6326,7 +6528,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>19</v>
@@ -6339,12 +6541,12 @@
         <v>41160.0</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>19</v>
@@ -6381,7 +6583,7 @@
         <v>0.0</v>
       </c>
       <c r="AD41" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="AI41" s="3">
         <v>0.0</v>
@@ -6428,7 +6630,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>28</v>
@@ -6448,13 +6650,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>14</v>
@@ -6468,7 +6670,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>28</v>
@@ -6488,7 +6690,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>28</v>
@@ -6499,7 +6701,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>30</v>
@@ -6519,13 +6721,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>14</v>
@@ -6534,12 +6736,12 @@
         <v>49</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>30</v>
@@ -6554,12 +6756,12 @@
         <v>49</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>30</v>
@@ -6579,7 +6781,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>30</v>
@@ -6592,12 +6794,12 @@
         <v>41286.0</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>30</v>
@@ -6634,7 +6836,7 @@
         <v>0.0</v>
       </c>
       <c r="AD51" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="AI51" s="3">
         <v>0.0</v>
@@ -6681,7 +6883,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>33</v>
@@ -6701,13 +6903,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>14</v>
@@ -6721,7 +6923,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>33</v>
@@ -6741,7 +6943,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>33</v>
@@ -6752,7 +6954,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>35</v>
@@ -6772,21 +6974,21 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>35</v>
@@ -6797,21 +6999,21 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>37</v>
@@ -6822,7 +7024,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>12</v>
@@ -6842,13 +7044,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>14</v>
@@ -6862,7 +7064,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>12</v>
@@ -6882,7 +7084,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>12</v>
@@ -6893,7 +7095,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>19</v>
@@ -6913,13 +7115,13 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>14</v>
@@ -6933,7 +7135,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>19</v>
@@ -6953,7 +7155,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>19</v>
@@ -6973,7 +7175,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>19</v>
@@ -6984,7 +7186,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>28</v>
@@ -7004,13 +7206,13 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>14</v>
@@ -7019,12 +7221,12 @@
         <v>49</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>28</v>
@@ -7039,12 +7241,12 @@
         <v>49</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>28</v>
@@ -7057,12 +7259,12 @@
         <v>41264.0</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>28</v>
@@ -7099,7 +7301,7 @@
         <v>0.0</v>
       </c>
       <c r="AD74" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="AI74" s="3">
         <v>0.0</v>
@@ -7146,7 +7348,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>30</v>
@@ -7166,13 +7368,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>14</v>
@@ -7186,7 +7388,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>30</v>
@@ -7206,7 +7408,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>30</v>
@@ -7217,7 +7419,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>33</v>
@@ -7237,13 +7439,13 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>14</v>
@@ -7257,7 +7459,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>33</v>
@@ -7277,7 +7479,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>33</v>
@@ -7288,7 +7490,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>35</v>
@@ -7308,21 +7510,21 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>35</v>
@@ -7333,21 +7535,21 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>37</v>
@@ -7358,7 +7560,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>12</v>
@@ -7378,13 +7580,13 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>14</v>
@@ -7398,7 +7600,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>12</v>
@@ -7409,7 +7611,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>19</v>
@@ -7429,21 +7631,21 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>19</v>
@@ -7463,7 +7665,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>19</v>
@@ -7483,7 +7685,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>19</v>
@@ -7494,7 +7696,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>28</v>
@@ -7514,13 +7716,13 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>14</v>
@@ -7534,7 +7736,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>28</v>
@@ -7554,7 +7756,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>28</v>
@@ -7565,7 +7767,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>30</v>
@@ -7585,13 +7787,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>14</v>
@@ -7605,7 +7807,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>30</v>
@@ -7625,7 +7827,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>30</v>
@@ -7645,7 +7847,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>30</v>
@@ -7656,7 +7858,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>33</v>
@@ -7676,13 +7878,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>14</v>
@@ -7696,7 +7898,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>33</v>
@@ -7716,7 +7918,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>33</v>
@@ -7727,7 +7929,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>35</v>
@@ -7747,21 +7949,21 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>35</v>
@@ -7772,21 +7974,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>37</v>
@@ -7797,7 +7999,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>12</v>
@@ -7817,13 +8019,13 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>14</v>
@@ -7837,7 +8039,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>12</v>
@@ -7857,7 +8059,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>12</v>
@@ -7868,7 +8070,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>19</v>
@@ -7888,13 +8090,13 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>14</v>
@@ -7908,7 +8110,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>19</v>
@@ -7928,19 +8130,19 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>14</v>
@@ -7948,7 +8150,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>19</v>
@@ -7957,7 +8159,7 @@
         <v>23</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>25</v>
@@ -7968,7 +8170,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>19</v>
@@ -8026,21 +8228,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>37</v>
@@ -8051,7 +8253,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -8071,13 +8273,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
@@ -8091,7 +8293,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
@@ -8111,7 +8313,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -8122,7 +8324,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
@@ -8134,35 +8336,35 @@
         <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>19</v>
@@ -8174,15 +8376,15 @@
         <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>19</v>
@@ -8202,7 +8404,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>19</v>
@@ -8213,7 +8415,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>28</v>
@@ -8233,13 +8435,13 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
@@ -8253,7 +8455,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>28</v>
@@ -8264,7 +8466,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>30</v>
@@ -8284,13 +8486,13 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>14</v>
@@ -8304,7 +8506,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>30</v>
@@ -8324,7 +8526,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
@@ -8335,7 +8537,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>33</v>
@@ -8355,13 +8557,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>14</v>
@@ -8375,7 +8577,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>33</v>
@@ -8395,7 +8597,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>33</v>
@@ -8406,7 +8608,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>35</v>
@@ -8426,21 +8628,21 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>35</v>
@@ -8451,21 +8653,21 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>37</v>
@@ -8476,7 +8678,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>12</v>
@@ -8496,13 +8698,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>14</v>
@@ -8516,7 +8718,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>12</v>
@@ -8536,7 +8738,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -8547,7 +8749,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>19</v>
@@ -8562,18 +8764,18 @@
         <v>49</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>14</v>
@@ -8582,12 +8784,12 @@
         <v>49</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>19</v>
@@ -8602,12 +8804,12 @@
         <v>49</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>19</v>
@@ -8627,7 +8829,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>19</v>
@@ -8638,7 +8840,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>28</v>
@@ -8658,13 +8860,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>14</v>
@@ -8678,7 +8880,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>28</v>
@@ -8698,7 +8900,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>28</v>
@@ -8709,7 +8911,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>30</v>
@@ -8721,35 +8923,35 @@
         <v>14</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="G43" s="2" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>30</v>
@@ -8761,15 +8963,15 @@
         <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>30</v>
@@ -8789,7 +8991,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>30</v>
@@ -8800,7 +9002,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>33</v>
@@ -8815,18 +9017,18 @@
         <v>49</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>14</v>
@@ -8835,12 +9037,12 @@
         <v>49</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>33</v>
@@ -8851,7 +9053,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>35</v>
@@ -8871,21 +9073,21 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>35</v>
@@ -8896,21 +9098,21 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>37</v>
@@ -8921,7 +9123,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>12</v>
@@ -8941,13 +9143,13 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>14</v>
@@ -8961,7 +9163,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>12</v>
@@ -8981,7 +9183,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>12</v>
@@ -8992,7 +9194,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>19</v>
@@ -9012,13 +9214,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>14</v>
@@ -9032,7 +9234,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>19</v>
@@ -9052,7 +9254,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>19</v>
@@ -9072,7 +9274,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>19</v>
@@ -9083,7 +9285,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>28</v>
@@ -9103,13 +9305,13 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>14</v>
@@ -9123,7 +9325,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>28</v>
@@ -9143,7 +9345,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>28</v>
@@ -9154,7 +9356,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>30</v>
@@ -9169,18 +9371,18 @@
         <v>49</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>14</v>
@@ -9189,12 +9391,12 @@
         <v>49</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>30</v>
@@ -9209,12 +9411,12 @@
         <v>49</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>30</v>
@@ -9234,7 +9436,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>30</v>
@@ -9245,7 +9447,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>33</v>
@@ -9265,13 +9467,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>14</v>
@@ -9285,7 +9487,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>33</v>
@@ -9305,7 +9507,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>33</v>
@@ -9316,7 +9518,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>35</v>
@@ -9336,21 +9538,21 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>35</v>
@@ -9361,21 +9563,21 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>37</v>
@@ -9386,7 +9588,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>12</v>
@@ -9406,13 +9608,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>14</v>
@@ -9426,7 +9628,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>12</v>
@@ -9446,7 +9648,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>12</v>
@@ -9457,7 +9659,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>19</v>
@@ -9477,13 +9679,13 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>14</v>
@@ -9497,7 +9699,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>19</v>
@@ -9517,7 +9719,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>19</v>
@@ -9537,7 +9739,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>19</v>
@@ -9548,7 +9750,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>28</v>
@@ -9568,13 +9770,13 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>14</v>
@@ -9588,7 +9790,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>28</v>
@@ -9608,7 +9810,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>28</v>
@@ -9619,7 +9821,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>30</v>
@@ -9634,26 +9836,26 @@
         <v>49</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>30</v>
@@ -9668,12 +9870,12 @@
         <v>49</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>30</v>
@@ -9693,7 +9895,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>30</v>
@@ -9704,7 +9906,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>33</v>
@@ -9724,13 +9926,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>14</v>
@@ -9744,7 +9946,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>33</v>
@@ -9764,7 +9966,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>33</v>
@@ -9775,21 +9977,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>35</v>
@@ -9809,7 +10011,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>35</v>
@@ -9867,7 +10069,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>30</v>
@@ -9876,12 +10078,12 @@
         <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>30</v>
@@ -9892,13 +10094,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
@@ -9912,7 +10114,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>33</v>
@@ -9932,13 +10134,13 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>14</v>
@@ -9952,7 +10154,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>33</v>
@@ -9963,7 +10165,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>35</v>
@@ -9983,7 +10185,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>35</v>
@@ -9992,12 +10194,12 @@
         <v>17</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>35</v>
@@ -10008,7 +10210,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>37</v>
@@ -10017,12 +10219,12 @@
         <v>17</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>37</v>
@@ -10033,7 +10235,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
@@ -10053,7 +10255,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
@@ -10073,13 +10275,13 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>14</v>
@@ -10093,7 +10295,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>12</v>
@@ -10104,7 +10306,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>19</v>
@@ -10124,7 +10326,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>19</v>
@@ -10144,13 +10346,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>14</v>
@@ -10164,7 +10366,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>19</v>
@@ -10184,7 +10386,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>19</v>
@@ -10195,7 +10397,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>28</v>
@@ -10215,7 +10417,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>28</v>
@@ -10235,13 +10437,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>14</v>
@@ -10255,7 +10457,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>28</v>
@@ -10266,7 +10468,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>30</v>
@@ -10286,7 +10488,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>30</v>
@@ -10306,13 +10508,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>14</v>
@@ -10326,7 +10528,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>30</v>
@@ -10338,15 +10540,15 @@
         <v>24</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>30</v>
@@ -10357,7 +10559,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>33</v>
@@ -10377,13 +10579,13 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>14</v>
@@ -10397,7 +10599,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>33</v>
@@ -10417,7 +10619,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>33</v>
@@ -10428,7 +10630,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>35</v>
@@ -10448,21 +10650,21 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>35</v>
@@ -10473,21 +10675,21 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>37</v>
@@ -10498,7 +10700,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>12</v>
@@ -10518,13 +10720,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>14</v>
@@ -10538,7 +10740,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>12</v>
@@ -10549,7 +10751,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>19</v>
@@ -10564,18 +10766,18 @@
         <v>49</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>14</v>
@@ -10584,12 +10786,12 @@
         <v>49</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>19</v>
@@ -10609,7 +10811,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>19</v>
@@ -10620,7 +10822,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>28</v>
@@ -10635,18 +10837,18 @@
         <v>49</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>14</v>
@@ -10655,12 +10857,12 @@
         <v>49</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>28</v>
@@ -10671,7 +10873,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>30</v>
@@ -10686,18 +10888,18 @@
         <v>49</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>14</v>
@@ -10706,12 +10908,12 @@
         <v>49</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>30</v>
@@ -10726,12 +10928,12 @@
         <v>24</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>30</v>
@@ -10743,15 +10945,15 @@
         <v>24</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>30</v>
@@ -10762,7 +10964,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>33</v>
@@ -10782,13 +10984,13 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>14</v>
@@ -10802,7 +11004,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>33</v>
@@ -10822,7 +11024,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>33</v>
@@ -10833,7 +11035,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>35</v>
@@ -10853,21 +11055,21 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>35</v>
@@ -10878,21 +11080,21 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>37</v>
@@ -10903,7 +11105,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>12</v>
@@ -10923,13 +11125,13 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>14</v>
@@ -10943,7 +11145,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>12</v>
@@ -10954,7 +11156,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>19</v>
@@ -10974,13 +11176,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>14</v>
@@ -10994,7 +11196,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>19</v>
@@ -11014,7 +11216,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>19</v>
@@ -11034,7 +11236,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>19</v>
@@ -11045,7 +11247,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>28</v>
@@ -11065,13 +11267,13 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>14</v>
@@ -11085,7 +11287,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>28</v>
@@ -11100,12 +11302,12 @@
         <v>21</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>28</v>
@@ -11116,7 +11318,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>30</v>
@@ -11136,13 +11338,13 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>14</v>
@@ -11156,7 +11358,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>30</v>
@@ -11176,7 +11378,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>30</v>
@@ -11187,7 +11389,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>33</v>
@@ -11202,18 +11404,18 @@
         <v>49</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>14</v>
@@ -11222,12 +11424,12 @@
         <v>49</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>33</v>
@@ -11238,7 +11440,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>35</v>
@@ -11258,7 +11460,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>35</v>
@@ -11269,7 +11471,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>37</v>
@@ -11280,7 +11482,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>12</v>
@@ -11300,13 +11502,13 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>14</v>
@@ -11320,7 +11522,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>12</v>
@@ -11340,7 +11542,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>12</v>
@@ -11351,7 +11553,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>19</v>
@@ -11371,13 +11573,13 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>14</v>
@@ -11391,7 +11593,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>19</v>
@@ -11411,7 +11613,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>19</v>
@@ -11431,7 +11633,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>19</v>
@@ -11442,7 +11644,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>28</v>
@@ -11462,13 +11664,13 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>14</v>
@@ -11482,7 +11684,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>28</v>
@@ -11502,7 +11704,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>28</v>
@@ -11513,7 +11715,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>30</v>
@@ -11533,13 +11735,13 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>14</v>
@@ -11553,7 +11755,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>30</v>
@@ -11573,7 +11775,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>30</v>
@@ -11593,7 +11795,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>30</v>
@@ -11604,7 +11806,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>33</v>
@@ -11624,13 +11826,13 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>14</v>
@@ -11644,7 +11846,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>33</v>
@@ -11664,7 +11866,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>33</v>
@@ -11675,21 +11877,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>35</v>
@@ -11709,7 +11911,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>35</v>

--- a/google_data/Pobočky/Výroba/Databaze Výroba 2026.xlsx
+++ b/google_data/Pobočky/Výroba/Databaze Výroba 2026.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2921" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3079" uniqueCount="238">
   <si>
     <t>Datum</t>
   </si>
@@ -205,6 +205,45 @@
     <t>20.06.2026</t>
   </si>
   <si>
+    <t>21.06.2026</t>
+  </si>
+  <si>
+    <t>22.06.2026</t>
+  </si>
+  <si>
+    <t>23.06.2026</t>
+  </si>
+  <si>
+    <t>24.06.2026</t>
+  </si>
+  <si>
+    <t>25.06.2026</t>
+  </si>
+  <si>
+    <t>26.06.2026</t>
+  </si>
+  <si>
+    <t>27.06.2026</t>
+  </si>
+  <si>
+    <t>28.06.2026</t>
+  </si>
+  <si>
+    <t>29.06.2026</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>Koteliuk Maryna</t>
+  </si>
+  <si>
+    <t>30.06.2026</t>
+  </si>
+  <si>
     <t>01.05.2026</t>
   </si>
   <si>
@@ -247,9 +286,6 @@
     <t>12.05.2026</t>
   </si>
   <si>
-    <t>07:00</t>
-  </si>
-  <si>
     <t>13.05.2026</t>
   </si>
   <si>
@@ -356,9 +392,6 @@
   </si>
   <si>
     <t>14.04.2026</t>
-  </si>
-  <si>
-    <t>17:00</t>
   </si>
   <si>
     <t>23:00</t>
@@ -2251,6 +2284,576 @@
         <v>40784.0</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H72" s="3">
+        <v>40004.0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H76" s="3">
+        <v>41709.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80" s="3">
+        <v>41452.0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H83" s="3">
+        <v>40713.75</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H87" s="3">
+        <v>41192.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H91" s="3">
+        <v>41614.75</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H93" s="3">
+        <v>40784.0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H94" s="3">
+        <v>40004.0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H99" s="3">
+        <v>41136.5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H104" s="3">
+        <v>43210.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2300,7 +2903,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>33</v>
@@ -2320,13 +2923,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -2340,7 +2943,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>33</v>
@@ -2360,7 +2963,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>33</v>
@@ -2371,7 +2974,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>35</v>
@@ -2391,7 +2994,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>35</v>
@@ -2402,7 +3005,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>37</v>
@@ -2413,7 +3016,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -2433,13 +3036,13 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -2453,7 +3056,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>12</v>
@@ -2473,7 +3076,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>12</v>
@@ -2484,13 +3087,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>14</v>
@@ -2504,7 +3107,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>19</v>
@@ -2524,7 +3127,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>19</v>
@@ -2544,7 +3147,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>19</v>
@@ -2555,7 +3158,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>28</v>
@@ -2575,13 +3178,13 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>14</v>
@@ -2595,7 +3198,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>28</v>
@@ -2606,7 +3209,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>30</v>
@@ -2626,13 +3229,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>14</v>
@@ -2646,7 +3249,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>30</v>
@@ -2666,7 +3269,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>30</v>
@@ -2686,7 +3289,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>30</v>
@@ -2697,13 +3300,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>14</v>
@@ -2717,7 +3320,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>33</v>
@@ -2737,7 +3340,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>33</v>
@@ -2748,7 +3351,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>35</v>
@@ -2769,7 +3372,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>35</v>
@@ -2803,7 +3406,7 @@
         <v>0.0</v>
       </c>
       <c r="AD29" s="1" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="AI29" s="3">
         <v>0.0</v>
@@ -2850,7 +3453,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>37</v>
@@ -2861,13 +3464,13 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>14</v>
@@ -2881,7 +3484,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -2901,7 +3504,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>12</v>
@@ -2912,13 +3515,13 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>14</v>
@@ -2927,12 +3530,12 @@
         <v>49</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>19</v>
@@ -2947,12 +3550,12 @@
         <v>49</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>19</v>
@@ -2972,7 +3575,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>19</v>
@@ -2983,13 +3586,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>14</v>
@@ -3003,7 +3606,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>28</v>
@@ -3023,7 +3626,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>28</v>
@@ -3034,13 +3637,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>14</v>
@@ -3054,7 +3657,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>30</v>
@@ -3074,7 +3677,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>30</v>
@@ -3094,7 +3697,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>30</v>
@@ -3105,13 +3708,13 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>14</v>
@@ -3125,7 +3728,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>33</v>
@@ -3145,7 +3748,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>33</v>
@@ -3156,7 +3759,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>35</v>
@@ -3167,7 +3770,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>37</v>
@@ -3178,7 +3781,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>12</v>
@@ -3198,13 +3801,13 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>14</v>
@@ -3218,7 +3821,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>12</v>
@@ -3229,7 +3832,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>19</v>
@@ -3249,13 +3852,13 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>14</v>
@@ -3269,7 +3872,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>19</v>
@@ -3289,7 +3892,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>19</v>
@@ -3309,7 +3912,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>19</v>
@@ -3320,13 +3923,13 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>14</v>
@@ -3340,7 +3943,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>28</v>
@@ -3360,7 +3963,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>28</v>
@@ -3380,7 +3983,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>28</v>
@@ -3391,13 +3994,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>14</v>
@@ -3411,7 +4014,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>30</v>
@@ -3431,7 +4034,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>30</v>
@@ -3451,7 +4054,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>30</v>
@@ -3471,7 +4074,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>30</v>
@@ -3482,7 +4085,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>33</v>
@@ -3502,13 +4105,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>14</v>
@@ -3522,7 +4125,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>33</v>
@@ -3542,7 +4145,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>33</v>
@@ -3553,7 +4156,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>35</v>
@@ -3573,7 +4176,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>35</v>
@@ -3584,7 +4187,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>37</v>
@@ -3595,7 +4198,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>12</v>
@@ -3615,7 +4218,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>12</v>
@@ -3635,7 +4238,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>12</v>
@@ -3646,7 +4249,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>19</v>
@@ -3666,7 +4269,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>19</v>
@@ -3686,7 +4289,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>19</v>
@@ -3706,7 +4309,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>19</v>
@@ -3717,7 +4320,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>28</v>
@@ -3737,7 +4340,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>28</v>
@@ -3757,7 +4360,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>28</v>
@@ -3768,7 +4371,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>30</v>
@@ -3788,7 +4391,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>30</v>
@@ -3808,7 +4411,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>30</v>
@@ -3828,7 +4431,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>30</v>
@@ -3839,7 +4442,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>33</v>
@@ -3859,7 +4462,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>33</v>
@@ -3879,7 +4482,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>33</v>
@@ -3890,7 +4493,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>35</v>
@@ -3910,7 +4513,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>35</v>
@@ -3921,7 +4524,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>37</v>
@@ -3979,7 +4582,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>28</v>
@@ -3999,13 +4602,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -4019,7 +4622,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>28</v>
@@ -4039,7 +4642,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>28</v>
@@ -4050,7 +4653,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>30</v>
@@ -4070,13 +4673,13 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>14</v>
@@ -4090,7 +4693,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>30</v>
@@ -4110,7 +4713,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>30</v>
@@ -4130,7 +4733,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>30</v>
@@ -4141,7 +4744,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>33</v>
@@ -4161,13 +4764,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -4181,7 +4784,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>33</v>
@@ -4201,7 +4804,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>33</v>
@@ -4212,7 +4815,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>35</v>
@@ -4232,7 +4835,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>35</v>
@@ -4243,7 +4846,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>37</v>
@@ -4254,7 +4857,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>12</v>
@@ -4274,13 +4877,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>14</v>
@@ -4294,7 +4897,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>12</v>
@@ -4314,7 +4917,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>12</v>
@@ -4325,7 +4928,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>19</v>
@@ -4345,13 +4948,13 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>14</v>
@@ -4365,7 +4968,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>19</v>
@@ -4385,13 +4988,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>24</v>
@@ -4400,12 +5003,12 @@
         <v>15</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>19</v>
@@ -4420,12 +5023,12 @@
         <v>25</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>19</v>
@@ -4436,7 +5039,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>28</v>
@@ -4456,13 +5059,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>14</v>
@@ -4476,7 +5079,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>28</v>
@@ -4496,7 +5099,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>28</v>
@@ -4507,7 +5110,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>30</v>
@@ -4527,13 +5130,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>14</v>
@@ -4547,7 +5150,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>30</v>
@@ -4567,7 +5170,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>30</v>
@@ -4587,7 +5190,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>30</v>
@@ -4598,7 +5201,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>33</v>
@@ -4613,18 +5216,18 @@
         <v>49</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>14</v>
@@ -4633,12 +5236,12 @@
         <v>49</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>33</v>
@@ -4653,12 +5256,12 @@
         <v>49</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>33</v>
@@ -4669,7 +5272,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>35</v>
@@ -4689,7 +5292,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>35</v>
@@ -4700,7 +5303,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>37</v>
@@ -4711,7 +5314,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>12</v>
@@ -4731,7 +5334,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>12</v>
@@ -4751,7 +5354,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>12</v>
@@ -4762,7 +5365,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>19</v>
@@ -4782,7 +5385,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>19</v>
@@ -4802,19 +5405,19 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>14</v>
@@ -4822,7 +5425,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>19</v>
@@ -4831,10 +5434,10 @@
         <v>23</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>14</v>
@@ -4842,7 +5445,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>19</v>
@@ -4853,13 +5456,13 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>14</v>
@@ -4873,7 +5476,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>28</v>
@@ -4893,7 +5496,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>28</v>
@@ -4913,7 +5516,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>28</v>
@@ -4924,7 +5527,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>30</v>
@@ -4944,13 +5547,13 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>14</v>
@@ -4964,7 +5567,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>30</v>
@@ -4984,7 +5587,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>30</v>
@@ -5004,7 +5607,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>30</v>
@@ -5015,7 +5618,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>33</v>
@@ -5035,13 +5638,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>14</v>
@@ -5055,7 +5658,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>33</v>
@@ -5066,7 +5669,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>35</v>
@@ -5086,7 +5689,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>35</v>
@@ -5097,7 +5700,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>37</v>
@@ -5108,7 +5711,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>12</v>
@@ -5128,13 +5731,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>14</v>
@@ -5148,7 +5751,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>12</v>
@@ -5159,7 +5762,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>19</v>
@@ -5179,13 +5782,13 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>14</v>
@@ -5199,19 +5802,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>14</v>
@@ -5219,7 +5822,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>19</v>
@@ -5228,18 +5831,18 @@
         <v>23</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>19</v>
@@ -5250,7 +5853,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>28</v>
@@ -5270,13 +5873,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>14</v>
@@ -5290,7 +5893,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>28</v>
@@ -5301,7 +5904,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>30</v>
@@ -5321,13 +5924,13 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>14</v>
@@ -5341,7 +5944,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>30</v>
@@ -5361,7 +5964,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>30</v>
@@ -5372,7 +5975,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>33</v>
@@ -5392,13 +5995,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>14</v>
@@ -5412,7 +6015,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>33</v>
@@ -5423,7 +6026,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>35</v>
@@ -5443,7 +6046,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>35</v>
@@ -5454,7 +6057,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>37</v>
@@ -5465,7 +6068,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>12</v>
@@ -5485,13 +6088,13 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>14</v>
@@ -5505,7 +6108,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>12</v>
@@ -5516,7 +6119,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>19</v>
@@ -5536,7 +6139,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>19</v>
@@ -5556,13 +6159,13 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>51</v>
@@ -5571,12 +6174,12 @@
         <v>60</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>19</v>
@@ -5585,18 +6188,18 @@
         <v>23</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>19</v>
@@ -5607,7 +6210,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>28</v>
@@ -5627,13 +6230,13 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>14</v>
@@ -5647,7 +6250,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>28</v>
@@ -5658,7 +6261,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>30</v>
@@ -5678,13 +6281,13 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>14</v>
@@ -5698,7 +6301,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>30</v>
@@ -5718,7 +6321,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>30</v>
@@ -5738,7 +6341,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>30</v>
@@ -5796,21 +6399,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>37</v>
@@ -5821,7 +6424,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -5841,13 +6444,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
@@ -5861,7 +6464,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
@@ -5881,7 +6484,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -5892,7 +6495,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
@@ -5912,13 +6515,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>14</v>
@@ -5932,7 +6535,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>19</v>
@@ -5947,12 +6550,12 @@
         <v>40</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>19</v>
@@ -5972,7 +6575,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>19</v>
@@ -5983,7 +6586,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>28</v>
@@ -6003,13 +6606,13 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
@@ -6023,7 +6626,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>28</v>
@@ -6043,7 +6646,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>28</v>
@@ -6054,7 +6657,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>30</v>
@@ -6074,13 +6677,13 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>14</v>
@@ -6094,7 +6697,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
@@ -6114,7 +6717,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>30</v>
@@ -6134,7 +6737,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>30</v>
@@ -6147,12 +6750,12 @@
         <v>40483.5</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>30</v>
@@ -6189,7 +6792,7 @@
         <v>0.0</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="AI22" s="3">
         <v>0.0</v>
@@ -6236,7 +6839,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>33</v>
@@ -6256,13 +6859,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>14</v>
@@ -6276,7 +6879,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>33</v>
@@ -6296,7 +6899,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>33</v>
@@ -6307,7 +6910,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>35</v>
@@ -6327,21 +6930,21 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>35</v>
@@ -6352,21 +6955,21 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>37</v>
@@ -6377,7 +6980,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -6397,13 +7000,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>14</v>
@@ -6417,7 +7020,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>12</v>
@@ -6437,7 +7040,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>12</v>
@@ -6448,7 +7051,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>19</v>
@@ -6468,13 +7071,13 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>14</v>
@@ -6483,12 +7086,12 @@
         <v>49</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>19</v>
@@ -6508,7 +7111,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>19</v>
@@ -6528,7 +7131,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>19</v>
@@ -6541,12 +7144,12 @@
         <v>41160.0</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>19</v>
@@ -6583,7 +7186,7 @@
         <v>0.0</v>
       </c>
       <c r="AD41" s="1" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="AI41" s="3">
         <v>0.0</v>
@@ -6630,7 +7233,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>28</v>
@@ -6650,13 +7253,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>14</v>
@@ -6670,7 +7273,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>28</v>
@@ -6690,7 +7293,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>28</v>
@@ -6701,7 +7304,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>30</v>
@@ -6721,13 +7324,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>14</v>
@@ -6736,12 +7339,12 @@
         <v>49</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>30</v>
@@ -6756,12 +7359,12 @@
         <v>49</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>30</v>
@@ -6781,7 +7384,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>30</v>
@@ -6794,12 +7397,12 @@
         <v>41286.0</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>30</v>
@@ -6836,7 +7439,7 @@
         <v>0.0</v>
       </c>
       <c r="AD51" s="1" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="AI51" s="3">
         <v>0.0</v>
@@ -6883,7 +7486,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>33</v>
@@ -6903,13 +7506,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>14</v>
@@ -6923,7 +7526,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>33</v>
@@ -6943,7 +7546,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>33</v>
@@ -6954,7 +7557,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>35</v>
@@ -6974,21 +7577,21 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>35</v>
@@ -6999,21 +7602,21 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>37</v>
@@ -7024,7 +7627,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>12</v>
@@ -7044,13 +7647,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>14</v>
@@ -7064,7 +7667,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>12</v>
@@ -7084,7 +7687,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>12</v>
@@ -7095,7 +7698,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>19</v>
@@ -7115,13 +7718,13 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>14</v>
@@ -7135,7 +7738,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>19</v>
@@ -7155,7 +7758,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>19</v>
@@ -7175,7 +7778,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>19</v>
@@ -7186,7 +7789,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>28</v>
@@ -7206,13 +7809,13 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>14</v>
@@ -7221,12 +7824,12 @@
         <v>49</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>28</v>
@@ -7241,12 +7844,12 @@
         <v>49</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>28</v>
@@ -7259,12 +7862,12 @@
         <v>41264.0</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>28</v>
@@ -7301,7 +7904,7 @@
         <v>0.0</v>
       </c>
       <c r="AD74" s="1" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="AI74" s="3">
         <v>0.0</v>
@@ -7348,7 +7951,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>30</v>
@@ -7368,13 +7971,13 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>14</v>
@@ -7388,7 +7991,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>30</v>
@@ -7408,7 +8011,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>30</v>
@@ -7419,7 +8022,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>33</v>
@@ -7439,13 +8042,13 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>14</v>
@@ -7459,7 +8062,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>33</v>
@@ -7479,7 +8082,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>33</v>
@@ -7490,7 +8093,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>35</v>
@@ -7510,21 +8113,21 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>35</v>
@@ -7535,21 +8138,21 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>37</v>
@@ -7560,7 +8163,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>12</v>
@@ -7580,13 +8183,13 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>14</v>
@@ -7600,7 +8203,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>12</v>
@@ -7611,7 +8214,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>19</v>
@@ -7631,21 +8234,21 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>19</v>
@@ -7665,7 +8268,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>19</v>
@@ -7685,7 +8288,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>19</v>
@@ -7696,7 +8299,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>28</v>
@@ -7716,13 +8319,13 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>14</v>
@@ -7736,7 +8339,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>28</v>
@@ -7756,7 +8359,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>28</v>
@@ -7767,7 +8370,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>30</v>
@@ -7787,13 +8390,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>14</v>
@@ -7807,7 +8410,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>30</v>
@@ -7827,7 +8430,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>30</v>
@@ -7847,7 +8450,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>30</v>
@@ -7858,7 +8461,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>33</v>
@@ -7878,13 +8481,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>14</v>
@@ -7898,7 +8501,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>33</v>
@@ -7918,7 +8521,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>33</v>
@@ -7929,7 +8532,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>35</v>
@@ -7949,21 +8552,21 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>35</v>
@@ -7974,21 +8577,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>37</v>
@@ -7999,7 +8602,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>12</v>
@@ -8019,13 +8622,13 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>14</v>
@@ -8039,7 +8642,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>12</v>
@@ -8059,7 +8662,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>12</v>
@@ -8070,7 +8673,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>19</v>
@@ -8090,13 +8693,13 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>14</v>
@@ -8110,7 +8713,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>19</v>
@@ -8130,13 +8733,13 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>24</v>
@@ -8150,7 +8753,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>19</v>
@@ -8170,7 +8773,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>19</v>
@@ -8228,21 +8831,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>37</v>
@@ -8253,7 +8856,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -8273,13 +8876,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
@@ -8293,7 +8896,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
@@ -8313,7 +8916,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -8324,7 +8927,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
@@ -8344,13 +8947,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>14</v>
@@ -8364,7 +8967,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>19</v>
@@ -8384,7 +8987,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>19</v>
@@ -8404,7 +9007,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>19</v>
@@ -8415,7 +9018,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>28</v>
@@ -8435,13 +9038,13 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
@@ -8455,7 +9058,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>28</v>
@@ -8466,7 +9069,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>30</v>
@@ -8486,13 +9089,13 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>14</v>
@@ -8506,7 +9109,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>30</v>
@@ -8526,7 +9129,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
@@ -8537,7 +9140,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>33</v>
@@ -8557,13 +9160,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>14</v>
@@ -8577,7 +9180,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>33</v>
@@ -8597,7 +9200,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>33</v>
@@ -8608,7 +9211,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>35</v>
@@ -8628,21 +9231,21 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>35</v>
@@ -8653,21 +9256,21 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>37</v>
@@ -8678,7 +9281,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>12</v>
@@ -8698,13 +9301,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>14</v>
@@ -8718,7 +9321,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>12</v>
@@ -8738,7 +9341,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -8749,7 +9352,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>19</v>
@@ -8764,18 +9367,18 @@
         <v>49</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>14</v>
@@ -8784,12 +9387,12 @@
         <v>49</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>19</v>
@@ -8804,12 +9407,12 @@
         <v>49</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>19</v>
@@ -8829,7 +9432,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>19</v>
@@ -8840,7 +9443,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>28</v>
@@ -8860,13 +9463,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>14</v>
@@ -8880,7 +9483,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>28</v>
@@ -8900,7 +9503,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>28</v>
@@ -8911,7 +9514,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>30</v>
@@ -8931,13 +9534,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>14</v>
@@ -8951,7 +9554,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>30</v>
@@ -8971,7 +9574,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>30</v>
@@ -8991,7 +9594,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>30</v>
@@ -9002,7 +9605,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>33</v>
@@ -9017,18 +9620,18 @@
         <v>49</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>14</v>
@@ -9037,12 +9640,12 @@
         <v>49</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>33</v>
@@ -9053,7 +9656,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>35</v>
@@ -9073,21 +9676,21 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>35</v>
@@ -9098,21 +9701,21 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>37</v>
@@ -9123,7 +9726,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>12</v>
@@ -9143,13 +9746,13 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>14</v>
@@ -9163,7 +9766,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>12</v>
@@ -9183,7 +9786,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>12</v>
@@ -9194,7 +9797,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>19</v>
@@ -9214,13 +9817,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>14</v>
@@ -9234,7 +9837,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>19</v>
@@ -9254,7 +9857,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>19</v>
@@ -9274,7 +9877,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>19</v>
@@ -9285,7 +9888,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>28</v>
@@ -9305,13 +9908,13 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>14</v>
@@ -9325,7 +9928,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>28</v>
@@ -9345,7 +9948,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>28</v>
@@ -9356,7 +9959,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>30</v>
@@ -9371,18 +9974,18 @@
         <v>49</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>14</v>
@@ -9391,12 +9994,12 @@
         <v>49</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>30</v>
@@ -9411,12 +10014,12 @@
         <v>49</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>30</v>
@@ -9436,7 +10039,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>30</v>
@@ -9447,7 +10050,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>33</v>
@@ -9467,13 +10070,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>14</v>
@@ -9487,7 +10090,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>33</v>
@@ -9507,7 +10110,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>33</v>
@@ -9518,7 +10121,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>35</v>
@@ -9538,21 +10141,21 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>35</v>
@@ -9563,21 +10166,21 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>37</v>
@@ -9588,7 +10191,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>12</v>
@@ -9608,13 +10211,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>14</v>
@@ -9628,7 +10231,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>12</v>
@@ -9648,7 +10251,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>12</v>
@@ -9659,7 +10262,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>19</v>
@@ -9679,13 +10282,13 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>14</v>
@@ -9699,7 +10302,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>19</v>
@@ -9719,7 +10322,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>19</v>
@@ -9739,7 +10342,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>19</v>
@@ -9750,7 +10353,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>28</v>
@@ -9770,13 +10373,13 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>14</v>
@@ -9790,7 +10393,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>28</v>
@@ -9810,7 +10413,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>28</v>
@@ -9821,7 +10424,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>30</v>
@@ -9836,26 +10439,26 @@
         <v>49</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>30</v>
@@ -9870,12 +10473,12 @@
         <v>49</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>30</v>
@@ -9895,7 +10498,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>30</v>
@@ -9906,7 +10509,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>33</v>
@@ -9926,13 +10529,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>14</v>
@@ -9946,7 +10549,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>33</v>
@@ -9966,7 +10569,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>33</v>
@@ -9977,21 +10580,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>35</v>
@@ -10011,7 +10614,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>35</v>
@@ -10069,7 +10672,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>30</v>
@@ -10078,12 +10681,12 @@
         <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>30</v>
@@ -10094,13 +10697,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
@@ -10114,7 +10717,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>33</v>
@@ -10134,13 +10737,13 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>14</v>
@@ -10154,7 +10757,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>33</v>
@@ -10165,7 +10768,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>35</v>
@@ -10185,7 +10788,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>35</v>
@@ -10194,12 +10797,12 @@
         <v>17</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>35</v>
@@ -10210,7 +10813,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>37</v>
@@ -10219,12 +10822,12 @@
         <v>17</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>37</v>
@@ -10235,7 +10838,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
@@ -10255,7 +10858,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
@@ -10275,13 +10878,13 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>14</v>
@@ -10295,7 +10898,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>12</v>
@@ -10306,7 +10909,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>19</v>
@@ -10326,7 +10929,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>19</v>
@@ -10346,13 +10949,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>14</v>
@@ -10366,7 +10969,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>19</v>
@@ -10386,7 +10989,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>19</v>
@@ -10397,7 +11000,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>28</v>
@@ -10417,7 +11020,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>28</v>
@@ -10437,13 +11040,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>14</v>
@@ -10457,7 +11060,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>28</v>
@@ -10468,7 +11071,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>30</v>
@@ -10488,7 +11091,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>30</v>
@@ -10508,13 +11111,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>14</v>
@@ -10528,7 +11131,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>30</v>
@@ -10540,15 +11143,15 @@
         <v>24</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>30</v>
@@ -10559,7 +11162,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>33</v>
@@ -10579,13 +11182,13 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>14</v>
@@ -10599,7 +11202,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>33</v>
@@ -10619,7 +11222,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>33</v>
@@ -10630,7 +11233,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>35</v>
@@ -10650,21 +11253,21 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>35</v>
@@ -10675,21 +11278,21 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>37</v>
@@ -10700,7 +11303,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>12</v>
@@ -10720,13 +11323,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>14</v>
@@ -10740,7 +11343,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>12</v>
@@ -10751,7 +11354,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>19</v>
@@ -10766,18 +11369,18 @@
         <v>49</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>14</v>
@@ -10786,12 +11389,12 @@
         <v>49</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>19</v>
@@ -10811,7 +11414,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>19</v>
@@ -10822,7 +11425,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>28</v>
@@ -10837,18 +11440,18 @@
         <v>49</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>14</v>
@@ -10857,12 +11460,12 @@
         <v>49</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>28</v>
@@ -10873,7 +11476,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>30</v>
@@ -10888,18 +11491,18 @@
         <v>49</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>14</v>
@@ -10908,12 +11511,12 @@
         <v>49</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>30</v>
@@ -10928,12 +11531,12 @@
         <v>24</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>30</v>
@@ -10945,15 +11548,15 @@
         <v>24</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>30</v>
@@ -10964,7 +11567,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>33</v>
@@ -10984,13 +11587,13 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>14</v>
@@ -11004,7 +11607,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>33</v>
@@ -11024,7 +11627,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>33</v>
@@ -11035,7 +11638,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>35</v>
@@ -11055,21 +11658,21 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>35</v>
@@ -11080,21 +11683,21 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>37</v>
@@ -11105,7 +11708,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>12</v>
@@ -11125,13 +11728,13 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>14</v>
@@ -11145,7 +11748,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>12</v>
@@ -11156,7 +11759,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>19</v>
@@ -11176,13 +11779,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>14</v>
@@ -11196,7 +11799,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>19</v>
@@ -11216,7 +11819,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>19</v>
@@ -11236,7 +11839,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>19</v>
@@ -11247,7 +11850,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>28</v>
@@ -11267,13 +11870,13 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>14</v>
@@ -11287,7 +11890,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>28</v>
@@ -11302,12 +11905,12 @@
         <v>21</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>28</v>
@@ -11318,7 +11921,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>30</v>
@@ -11338,13 +11941,13 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>14</v>
@@ -11358,7 +11961,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>30</v>
@@ -11378,7 +11981,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>30</v>
@@ -11389,7 +11992,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>33</v>
@@ -11404,18 +12007,18 @@
         <v>49</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>14</v>
@@ -11424,12 +12027,12 @@
         <v>49</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>33</v>
@@ -11440,7 +12043,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>35</v>
@@ -11460,7 +12063,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>35</v>
@@ -11471,7 +12074,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>37</v>
@@ -11482,7 +12085,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>12</v>
@@ -11502,13 +12105,13 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>14</v>
@@ -11522,7 +12125,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>12</v>
@@ -11542,7 +12145,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>12</v>
@@ -11553,7 +12156,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>19</v>
@@ -11573,13 +12176,13 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>14</v>
@@ -11593,7 +12196,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>19</v>
@@ -11613,7 +12216,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>19</v>
@@ -11633,7 +12236,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>19</v>
@@ -11644,7 +12247,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>28</v>
@@ -11664,13 +12267,13 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>14</v>
@@ -11684,7 +12287,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>28</v>
@@ -11704,7 +12307,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>28</v>
@@ -11715,7 +12318,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>30</v>
@@ -11735,13 +12338,13 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>14</v>
@@ -11755,7 +12358,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>30</v>
@@ -11775,7 +12378,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>30</v>
@@ -11795,7 +12398,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>30</v>
@@ -11806,7 +12409,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>33</v>
@@ -11826,13 +12429,13 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>14</v>
@@ -11846,7 +12449,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>33</v>
@@ -11866,7 +12469,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>33</v>
@@ -11877,21 +12480,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>35</v>
@@ -11911,7 +12514,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>35</v>
